--- a/docs/plans/analysis-table-mapping.xlsx
+++ b/docs/plans/analysis-table-mapping.xlsx
@@ -15,7 +15,6 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'候选总表'!$A$2:$F$1176</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'待裁决项'!$A$1:$H$10</definedName>
   </definedNames>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
@@ -29,7 +28,7 @@
     <numFmt numFmtId="166" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="38">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -264,8 +263,16 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000D47A1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0001579B"/>
+    </font>
   </fonts>
-  <fills count="44">
+  <fills count="45">
     <fill>
       <patternFill/>
     </fill>
@@ -512,6 +519,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E1F5FE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3F2FD"/>
       </patternFill>
     </fill>
   </fills>
@@ -805,7 +817,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -893,6 +905,12 @@
     </xf>
     <xf numFmtId="0" fontId="35" fillId="43" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="44" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="43" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -36697,7 +36715,7 @@
       </c>
       <c r="C3" s="24" t="inlineStr">
         <is>
-          <t>LOA001（MC001）</t>
+          <t>品号</t>
         </is>
       </c>
       <c r="D3" s="27" t="inlineStr">
@@ -36712,7 +36730,7 @@
       </c>
       <c r="F3" s="28" t="inlineStr">
         <is>
-          <t>易助=品号；易飞 INVMC.MC001=品号</t>
+          <t>直接对应</t>
         </is>
       </c>
     </row>
@@ -36729,7 +36747,7 @@
       </c>
       <c r="C4" s="25" t="inlineStr">
         <is>
-          <t>LOA002（MC002）</t>
+          <t>仓库</t>
         </is>
       </c>
       <c r="D4" s="27" t="inlineStr">
@@ -36744,7 +36762,7 @@
       </c>
       <c r="F4" s="28" t="inlineStr">
         <is>
-          <t>易助=仓库；易飞 MC002=仓库</t>
+          <t>直接对应</t>
         </is>
       </c>
     </row>
@@ -36761,7 +36779,7 @@
       </c>
       <c r="C5" s="24" t="inlineStr">
         <is>
-          <t>LOA003（MC007）</t>
+          <t>库存数量</t>
         </is>
       </c>
       <c r="D5" s="27" t="inlineStr">
@@ -36776,7 +36794,7 @@
       </c>
       <c r="F5" s="28" t="inlineStr">
         <is>
-          <t>易助=现有库存量；易飞 MC007=库存数量</t>
+          <t>直接对应。易飞 INVMC 即现有库存量档</t>
         </is>
       </c>
     </row>
@@ -36793,7 +36811,7 @@
       </c>
       <c r="C6" s="25" t="inlineStr">
         <is>
-          <t>LOA004（MC008）</t>
+          <t>库存金额</t>
         </is>
       </c>
       <c r="D6" s="27" t="inlineStr">
@@ -36808,7 +36826,7 @@
       </c>
       <c r="F6" s="28" t="inlineStr">
         <is>
-          <t>易助=现有库存成本；易飞 MC008=库存金额</t>
+          <t>直接对应（成本在 MC008，非 INVML）</t>
         </is>
       </c>
     </row>
@@ -36825,12 +36843,12 @@
       </c>
       <c r="C7" s="24" t="inlineStr">
         <is>
-          <t>LPA001（LB001）</t>
+          <t>品号</t>
         </is>
       </c>
       <c r="D7" s="27" t="inlineStr">
         <is>
-          <t>LB001</t>
+          <t>LC001</t>
         </is>
       </c>
       <c r="E7" s="27" t="inlineStr">
@@ -36840,7 +36858,7 @@
       </c>
       <c r="F7" s="28" t="inlineStr">
         <is>
-          <t>直接对应</t>
+          <t>INVLC 维度=品号+年月+仓库，按品号汇总即得</t>
         </is>
       </c>
     </row>
@@ -36857,12 +36875,12 @@
       </c>
       <c r="C8" s="25" t="inlineStr">
         <is>
-          <t>LPA002（LB002）</t>
+          <t>库存年月</t>
         </is>
       </c>
       <c r="D8" s="27" t="inlineStr">
         <is>
-          <t>LB002</t>
+          <t>LC002</t>
         </is>
       </c>
       <c r="E8" s="27" t="inlineStr">
@@ -36872,7 +36890,7 @@
       </c>
       <c r="F8" s="28" t="inlineStr">
         <is>
-          <t>易助=年月；易飞 LB002=库存年月</t>
+          <t>直接对应</t>
         </is>
       </c>
     </row>
@@ -36889,22 +36907,22 @@
       </c>
       <c r="C9" s="24" t="inlineStr">
         <is>
-          <t>月初总数量 LB003 + 本月异动</t>
-        </is>
-      </c>
-      <c r="D9" s="29" t="inlineStr">
-        <is>
-          <t>(需计算)</t>
-        </is>
-      </c>
-      <c r="E9" s="29" t="inlineStr">
-        <is>
-          <t>需换列</t>
+          <t>期末数量</t>
+        </is>
+      </c>
+      <c r="D9" s="36" t="inlineStr">
+        <is>
+          <t>计算列</t>
+        </is>
+      </c>
+      <c r="E9" s="36" t="inlineStr">
+        <is>
+          <t>视图计算</t>
         </is>
       </c>
       <c r="F9" s="28" t="inlineStr">
         <is>
-          <t>易飞 INVLB 只有『月初』(LB003/LB004)，无期末列。期末=月初+当月INVLA异动净额，需视图计算</t>
+          <t>★ 用户裁决：期末需计算。实测链式校验 140/141 吻合。公式：SUM(LC004+LC006-LC008-LC010+LC012+LC014-LC016+LC018+LC020-LC022-LC024) GROUP BY LC001,LC002</t>
         </is>
       </c>
     </row>
@@ -36921,22 +36939,22 @@
       </c>
       <c r="C10" s="25" t="inlineStr">
         <is>
-          <t>月初总成本 LB004 + 本月异动</t>
-        </is>
-      </c>
-      <c r="D10" s="29" t="inlineStr">
-        <is>
-          <t>(需计算)</t>
-        </is>
-      </c>
-      <c r="E10" s="29" t="inlineStr">
-        <is>
-          <t>需换列</t>
+          <t>期末成本</t>
+        </is>
+      </c>
+      <c r="D10" s="36" t="inlineStr">
+        <is>
+          <t>计算列</t>
+        </is>
+      </c>
+      <c r="E10" s="36" t="inlineStr">
+        <is>
+          <t>视图计算</t>
         </is>
       </c>
       <c r="F10" s="28" t="inlineStr">
         <is>
-          <t>同 LPA003，期末成本需由 LB004 + INVLA.LA013 推算</t>
+          <t>★ 用户裁决：期末需计算。实测链式校验 141/141 精确吻合。公式：SUM(LC005+LC007-LC009-LC011+LC013+LC015-LC017+LC019+LC021-LC023-LC025) GROUP BY LC001,LC002</t>
         </is>
       </c>
     </row>
@@ -36953,22 +36971,22 @@
       </c>
       <c r="C11" s="24" t="inlineStr">
         <is>
-          <t>LPA005（LB010）</t>
-        </is>
-      </c>
-      <c r="D11" s="27" t="inlineStr">
-        <is>
-          <t>LB010</t>
-        </is>
-      </c>
-      <c r="E11" s="27" t="inlineStr">
-        <is>
-          <t>直接对应</t>
+          <t>平均单位成本</t>
+        </is>
+      </c>
+      <c r="D11" s="36" t="inlineStr">
+        <is>
+          <t>计算列</t>
+        </is>
+      </c>
+      <c r="E11" s="36" t="inlineStr">
+        <is>
+          <t>视图计算</t>
         </is>
       </c>
       <c r="F11" s="28" t="inlineStr">
         <is>
-          <t>易助=平均成本；易飞 LB010=单位成本。实测 LB010 有值(930/200/100)</t>
+          <t>易助 LPA005=平均成本 = 期末成本/期末数量。实测易飞 LC026~LC029 已有『本月成本-材料/人工/制费/加工』四要素可辅助拆分；但四要素不可加进期末公式（实测仅 88/141 吻合），仅作成本构成维度</t>
         </is>
       </c>
     </row>
@@ -36985,12 +37003,12 @@
       </c>
       <c r="C12" s="25" t="inlineStr">
         <is>
-          <t>LPB001（ML001 / LN001）</t>
+          <t>品号</t>
         </is>
       </c>
       <c r="D12" s="27" t="inlineStr">
         <is>
-          <t>ML001 / LN001</t>
+          <t>LE001</t>
         </is>
       </c>
       <c r="E12" s="27" t="inlineStr">
@@ -37000,7 +37018,7 @@
       </c>
       <c r="F12" s="28" t="inlineStr">
         <is>
-          <t>两表均以品号开头</t>
+          <t>INVLE 维度=品号+年月+仓库+库位+批号</t>
         </is>
       </c>
     </row>
@@ -37020,19 +37038,19 @@
           <t>库存年月</t>
         </is>
       </c>
-      <c r="D13" s="29" t="inlineStr">
-        <is>
-          <t>LN003</t>
-        </is>
-      </c>
-      <c r="E13" s="29" t="inlineStr">
-        <is>
-          <t>需换列</t>
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>LE002</t>
+        </is>
+      </c>
+      <c r="E13" s="27" t="inlineStr">
+        <is>
+          <t>直接对应</t>
         </is>
       </c>
       <c r="F13" s="28" t="inlineStr">
         <is>
-          <t>仅 INVLN 有库存年月；INVML 无年月列(是当前库存表)</t>
+          <t>直接对应</t>
         </is>
       </c>
     </row>
@@ -37049,12 +37067,12 @@
       </c>
       <c r="C14" s="25" t="inlineStr">
         <is>
-          <t>LPB003（ML002）</t>
+          <t>仓库</t>
         </is>
       </c>
       <c r="D14" s="27" t="inlineStr">
         <is>
-          <t>ML002</t>
+          <t>LE003</t>
         </is>
       </c>
       <c r="E14" s="27" t="inlineStr">
@@ -37064,7 +37082,7 @@
       </c>
       <c r="F14" s="28" t="inlineStr">
         <is>
-          <t>仅 INVML 有仓库；INVLN 无仓库列</t>
+          <t>直接对应</t>
         </is>
       </c>
     </row>
@@ -37081,22 +37099,22 @@
       </c>
       <c r="C15" s="24" t="inlineStr">
         <is>
-          <t>库存数量 / 月初总数量</t>
-        </is>
-      </c>
-      <c r="D15" s="29" t="inlineStr">
-        <is>
-          <t>ML005 / LN004</t>
-        </is>
-      </c>
-      <c r="E15" s="29" t="inlineStr">
-        <is>
-          <t>需换列</t>
+          <t>期末数量</t>
+        </is>
+      </c>
+      <c r="D15" s="36" t="inlineStr">
+        <is>
+          <t>计算列</t>
+        </is>
+      </c>
+      <c r="E15" s="36" t="inlineStr">
+        <is>
+          <t>视图计算</t>
         </is>
       </c>
       <c r="F15" s="28" t="inlineStr">
         <is>
-          <t>⚠ 两表均非『期末』：ML005=当前库存即时值，LN004=月初。期末需计算</t>
+          <t>★ 公式：LE006+LE008-LE010-LE012+LE014+LE016-LE018+LE020-LE022-LE024-LE026 （与 INVLC 同构，仅数量列奇数位；实测成本列 LE007~LE027 全为预留且恒零）</t>
         </is>
       </c>
     </row>
@@ -37118,7 +37136,7 @@
       </c>
       <c r="D16" s="30" t="inlineStr">
         <is>
-          <t>(无)</t>
+          <t>(需跨表)</t>
         </is>
       </c>
       <c r="E16" s="30" t="inlineStr">
@@ -37128,7 +37146,7 @@
       </c>
       <c r="F16" s="28" t="inlineStr">
         <is>
-          <t>⚠ P0：INVML 无任何成本列(实测 ML007/ML012~ML017 仅 ML012 非零346行但字典无中文名)，INVLN 有 LN005 月初总成本但无仓库维度</t>
+          <t>⚠ P0 仍在：用户已确认 INVLE/INVML 均『只有数量没有成本』（实测 LE007~LE031 全零）。仓库级期末成本只能由 INVLC.MC008 口径或 INVLA.LA013 汇总派生，批号级成本不可还原</t>
         </is>
       </c>
     </row>
@@ -37145,12 +37163,12 @@
       </c>
       <c r="C17" s="24" t="inlineStr">
         <is>
-          <t>LPB012（ML004 / LN002）</t>
+          <t>批号</t>
         </is>
       </c>
       <c r="D17" s="27" t="inlineStr">
         <is>
-          <t>ML004 / LN002</t>
+          <t>LE005</t>
         </is>
       </c>
       <c r="E17" s="27" t="inlineStr">
@@ -37160,7 +37178,7 @@
       </c>
       <c r="F17" s="28" t="inlineStr">
         <is>
-          <t>两表均有批号。实测易飞批号是真实值(非掩码)，优于易助 LPB012 全掩码问题</t>
+          <t>★ 用户裁决：期末相关走 INVLE。实测 LE005 为真实批号值；哨兵 `********************` 需转 NULL</t>
         </is>
       </c>
     </row>
@@ -37177,22 +37195,22 @@
       </c>
       <c r="C18" s="25" t="inlineStr">
         <is>
-          <t>单别</t>
-        </is>
-      </c>
-      <c r="D18" s="29" t="inlineStr">
-        <is>
-          <t>LA006</t>
-        </is>
-      </c>
-      <c r="E18" s="29" t="inlineStr">
-        <is>
-          <t>需换列</t>
+          <t>单据类型</t>
+        </is>
+      </c>
+      <c r="D18" s="27" t="inlineStr">
+        <is>
+          <t>CMSMQ.MQ003</t>
+        </is>
+      </c>
+      <c r="E18" s="27" t="inlineStr">
+        <is>
+          <t>直接对应</t>
         </is>
       </c>
       <c r="F18" s="28" t="inlineStr">
         <is>
-          <t>⚠ 语义升级：易助 LNA001=单据类型数字码('33'销货/'82'领料)；易飞 LA006=单别 char(4)(实测 130+ 种如 2301/023w/5401)。必须建单别码对照表，不能硬编码</t>
+          <t>★★ 用户裁决：LA006=单别（一种单据可有多个单别，单别+单号为唯一 key），LA006 关联 CMSMQ.MQ001 取 MQ003=具体单据类型（char(2)）。实测 INVLA 全部单别均可关联成功。→ 不硬编码单别码，走 CMSMQ 关联</t>
         </is>
       </c>
     </row>
@@ -37209,7 +37227,7 @@
       </c>
       <c r="C19" s="24" t="inlineStr">
         <is>
-          <t>LNA002（LA007）</t>
+          <t>单号</t>
         </is>
       </c>
       <c r="D19" s="27" t="inlineStr">
@@ -37224,7 +37242,7 @@
       </c>
       <c r="F19" s="28" t="inlineStr">
         <is>
-          <t>直接对应</t>
+          <t>直接对应（单别+单号=唯一 key，关联时须带 LA006）</t>
         </is>
       </c>
     </row>
@@ -37244,19 +37262,19 @@
           <t>入出别</t>
         </is>
       </c>
-      <c r="D20" s="29" t="inlineStr">
+      <c r="D20" s="27" t="inlineStr">
         <is>
           <t>LA005</t>
         </is>
       </c>
-      <c r="E20" s="29" t="inlineStr">
-        <is>
-          <t>需换列</t>
+      <c r="E20" s="27" t="inlineStr">
+        <is>
+          <t>直接对应</t>
         </is>
       </c>
       <c r="F20" s="28" t="inlineStr">
         <is>
-          <t>⚠ 类型升级：易助 LNA004='I'/'O' 字符；易飞 LA005=numeric ±1(实测 1:1174行 / -1:1158行)。SQL 需转换或改用 LA005</t>
+          <t>易飞 LA005=numeric ±1（实测 1:1174 / -1:1158），直接替代易助 'I'/'O'</t>
         </is>
       </c>
     </row>
@@ -37273,7 +37291,7 @@
       </c>
       <c r="C21" s="24" t="inlineStr">
         <is>
-          <t>LNA005（LA001）</t>
+          <t>品号</t>
         </is>
       </c>
       <c r="D21" s="27" t="inlineStr">
@@ -37305,7 +37323,7 @@
       </c>
       <c r="C22" s="25" t="inlineStr">
         <is>
-          <t>LNA006（LA004）</t>
+          <t>日期</t>
         </is>
       </c>
       <c r="D22" s="27" t="inlineStr">
@@ -37337,7 +37355,7 @@
       </c>
       <c r="C23" s="24" t="inlineStr">
         <is>
-          <t>LNA007（LA009）</t>
+          <t>仓库</t>
         </is>
       </c>
       <c r="D23" s="27" t="inlineStr">
@@ -37369,7 +37387,7 @@
       </c>
       <c r="C24" s="25" t="inlineStr">
         <is>
-          <t>LNA011（LA011）</t>
+          <t>单据交易库存数量</t>
         </is>
       </c>
       <c r="D24" s="27" t="inlineStr">
@@ -37401,7 +37419,7 @@
       </c>
       <c r="C25" s="24" t="inlineStr">
         <is>
-          <t>LNA013（LA013）</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="D25" s="27" t="inlineStr">
@@ -37436,19 +37454,19 @@
           <t>入出别</t>
         </is>
       </c>
-      <c r="D26" s="29" t="inlineStr">
+      <c r="D26" s="27" t="inlineStr">
         <is>
           <t>LA005</t>
         </is>
       </c>
-      <c r="E26" s="29" t="inlineStr">
-        <is>
-          <t>需换列</t>
+      <c r="E26" s="27" t="inlineStr">
+        <is>
+          <t>直接对应</t>
         </is>
       </c>
       <c r="F26" s="28" t="inlineStr">
         <is>
-          <t>★ 关键：易助 LNA015=加减项(±1)；易飞用 LA005 入出别 numeric ±1 直接表达。不需额外符号列，SQL 去掉 LNA015 乘数改乘 LA005</t>
+          <t>★ 易飞用 LA005 入出别 numeric ±1 直接表达加减项，不需额外符号列。SQL 去掉 LNA015 改乘 LA005</t>
         </is>
       </c>
     </row>
@@ -37465,22 +37483,22 @@
       </c>
       <c r="C27" s="24" t="inlineStr">
         <is>
-          <t>对象</t>
-        </is>
-      </c>
-      <c r="D27" s="30" t="inlineStr">
-        <is>
-          <t>LA024?</t>
-        </is>
-      </c>
-      <c r="E27" s="30" t="inlineStr">
-        <is>
-          <t>无等价列</t>
+          <t>客户编号</t>
+        </is>
+      </c>
+      <c r="D27" s="37" t="inlineStr">
+        <is>
+          <t>JOIN COPTG</t>
+        </is>
+      </c>
+      <c r="E27" s="37" t="inlineStr">
+        <is>
+          <t>关联取得</t>
         </is>
       </c>
       <c r="F27" s="28" t="inlineStr">
         <is>
-          <t>⚠ 易飞 LA024『对象』语义混杂：实测含客户名('天之蓝海更蓝')/供应商名('第一波供应商')/关联单号('5102-20260920002')。不可直接用作销货客户，建议改为 JOIN COPTG.TG004</t>
+          <t>★ 用户裁决单别+单号为 key 后，可由 LA006+LA007 关联 COPTG.TG004 取客户。比 LA024『对象』可靠（实测 LA024 混装客户名/供应商名/关联单号三类值）</t>
         </is>
       </c>
     </row>
@@ -37497,7 +37515,7 @@
       </c>
       <c r="C28" s="25" t="inlineStr">
         <is>
-          <t>LNA035（LA018）</t>
+          <t>金额-人工</t>
         </is>
       </c>
       <c r="D28" s="27" t="inlineStr">
@@ -37512,7 +37530,7 @@
       </c>
       <c r="F28" s="28" t="inlineStr">
         <is>
-          <t>★ 之前担心的『无等价列』不成立：易飞有完整成本四要素。实测 174 行非零</t>
+          <t>实测 174 行非零</t>
         </is>
       </c>
     </row>
@@ -37529,7 +37547,7 @@
       </c>
       <c r="C29" s="24" t="inlineStr">
         <is>
-          <t>LNA036（LA019）</t>
+          <t>金额-制费</t>
         </is>
       </c>
       <c r="D29" s="27" t="inlineStr">
@@ -37544,7 +37562,7 @@
       </c>
       <c r="F29" s="28" t="inlineStr">
         <is>
-          <t>★ 易飞=制费(=制造费用)。实测 174 行非零</t>
+          <t>实测 174 行非零</t>
         </is>
       </c>
     </row>
@@ -37564,19 +37582,19 @@
           <t>金额-加工</t>
         </is>
       </c>
-      <c r="D30" s="29" t="inlineStr">
+      <c r="D30" s="27" t="inlineStr">
         <is>
           <t>LA020</t>
         </is>
       </c>
-      <c r="E30" s="29" t="inlineStr">
-        <is>
-          <t>需换列</t>
+      <c r="E30" s="27" t="inlineStr">
+        <is>
+          <t>直接对应</t>
         </is>
       </c>
       <c r="F30" s="28" t="inlineStr">
         <is>
-          <t>⚠ 易助=委外成本；易飞=加工费用，无独立『委外』列。实测 229 行非零。口径需业务确认(委外是否归入加工)</t>
+          <t>易飞口径=加工费用（含委外）。实测 229 行非零。与 INVLC.LC029『本月成本-加工』同构，口径一致</t>
         </is>
       </c>
     </row>
@@ -37593,7 +37611,7 @@
       </c>
       <c r="C31" s="24" t="inlineStr">
         <is>
-          <t>KEA001（TG002）</t>
+          <t>单号</t>
         </is>
       </c>
       <c r="D31" s="27" t="inlineStr">
@@ -37625,7 +37643,7 @@
       </c>
       <c r="C32" s="25" t="inlineStr">
         <is>
-          <t>KEA003（TG003）</t>
+          <t>销货日期</t>
         </is>
       </c>
       <c r="D32" s="27" t="inlineStr">
@@ -37657,7 +37675,7 @@
       </c>
       <c r="C33" s="24" t="inlineStr">
         <is>
-          <t>KEA004（TG004）</t>
+          <t>客户编号</t>
         </is>
       </c>
       <c r="D33" s="27" t="inlineStr">
@@ -37704,7 +37722,7 @@
       </c>
       <c r="F34" s="28" t="inlineStr">
         <is>
-          <t>⚠ 易助 KEA023=无税金额(收入)；易飞 TG045 是含税总额，实测 10176.99=TG045，其税前=8853.98。收入口径应取 TG045-TG046，或直接用单身 COPTH.TH037 本币税前金额</t>
+          <t>⚠ 易飞 TG045 是含税额（实测 10176.99），易助要无税收入。改 TG045-TG046，或直接用单身 COPTH.TH037 本币税前金额</t>
         </is>
       </c>
     </row>
@@ -37721,7 +37739,7 @@
       </c>
       <c r="C35" s="24" t="inlineStr">
         <is>
-          <t>KEA040（TG023）</t>
+          <t>审核码</t>
         </is>
       </c>
       <c r="D35" s="27" t="inlineStr">
@@ -37736,7 +37754,7 @@
       </c>
       <c r="F35" s="28" t="inlineStr">
         <is>
-          <t>⚠ 取值差异：易助仅 'T'；易飞实测 Y(192)/N(108)/V(2)。V 含义待确认，默认只取 Y</t>
+          <t>★ 用户裁决：V=作废，统计只筛 ='Y'。模板默认值由 'T' 改 'Y'（实测 Y192/N108/V2）</t>
         </is>
       </c>
     </row>
@@ -37753,7 +37771,7 @@
       </c>
       <c r="C36" s="25" t="inlineStr">
         <is>
-          <t>KEB001（TH002）</t>
+          <t>单号</t>
         </is>
       </c>
       <c r="D36" s="27" t="inlineStr">
@@ -37785,7 +37803,7 @@
       </c>
       <c r="C37" s="24" t="inlineStr">
         <is>
-          <t>KEB003（TH004）</t>
+          <t>品号</t>
         </is>
       </c>
       <c r="D37" s="27" t="inlineStr">
@@ -37832,7 +37850,7 @@
       </c>
       <c r="F38" s="28" t="inlineStr">
         <is>
-          <t>⚠ 易助用 KEB011&gt;0 作过滤条件(与审核码并列)，语义疑似『实际出货量/已交量』。易飞最接近 TH008 数量，但无『已交量』列。需确认过滤意图</t>
+          <t>⚠ 易助用 KEB011&gt;0 作过滤条件（与审核码并列）。易飞无『已交量』列，最接近 TH008 数量。需确认过滤意图</t>
         </is>
       </c>
     </row>
@@ -37864,7 +37882,7 @@
       </c>
       <c r="F39" s="28" t="inlineStr">
         <is>
-          <t>⚠ 易助 KEB012=本币金额(收入)；易飞 TH013『金额』是含税(实测 10000)，TH037 才是税前(8849.56)。收入口径应取 TH037</t>
+          <t>⚠ 易飞 TH013『金额』是含税（实测 10000），TH037 才是税前（8849.56）。收入口径取 TH037</t>
         </is>
       </c>
     </row>
@@ -37881,7 +37899,7 @@
       </c>
       <c r="C40" s="25" t="inlineStr">
         <is>
-          <t>KEB021（TH020）</t>
+          <t>审核码</t>
         </is>
       </c>
       <c r="D40" s="27" t="inlineStr">
@@ -37896,7 +37914,7 @@
       </c>
       <c r="F40" s="28" t="inlineStr">
         <is>
-          <t>同 KEA040，Y/N/V 三值</t>
+          <t>V=作废，只取 ='Y'</t>
         </is>
       </c>
     </row>
@@ -37913,7 +37931,7 @@
       </c>
       <c r="C41" s="24" t="inlineStr">
         <is>
-          <t>JDA001（TG002）</t>
+          <t>单号</t>
         </is>
       </c>
       <c r="D41" s="27" t="inlineStr">
@@ -37945,7 +37963,7 @@
       </c>
       <c r="C42" s="25" t="inlineStr">
         <is>
-          <t>JDA003（TG003）</t>
+          <t>进货日期</t>
         </is>
       </c>
       <c r="D42" s="27" t="inlineStr">
@@ -37977,7 +37995,7 @@
       </c>
       <c r="C43" s="24" t="inlineStr">
         <is>
-          <t>JDA004（TG005）</t>
+          <t>供应商</t>
         </is>
       </c>
       <c r="D43" s="27" t="inlineStr">
@@ -38009,7 +38027,7 @@
       </c>
       <c r="C44" s="25" t="inlineStr">
         <is>
-          <t>JDA026（TG013）</t>
+          <t>审核码</t>
         </is>
       </c>
       <c r="D44" s="27" t="inlineStr">
@@ -38024,7 +38042,7 @@
       </c>
       <c r="F44" s="28" t="inlineStr">
         <is>
-          <t>Y(192)/N(108)/V(2)</t>
+          <t>V=作废，只取 ='Y'（实测 Y192/N108/V2）</t>
         </is>
       </c>
     </row>
@@ -38041,7 +38059,7 @@
       </c>
       <c r="C45" s="24" t="inlineStr">
         <is>
-          <t>JDB001（TH002）</t>
+          <t>单号</t>
         </is>
       </c>
       <c r="D45" s="27" t="inlineStr">
@@ -38073,7 +38091,7 @@
       </c>
       <c r="C46" s="25" t="inlineStr">
         <is>
-          <t>JDB003（TH004）</t>
+          <t>品号</t>
         </is>
       </c>
       <c r="D46" s="27" t="inlineStr">
@@ -38105,7 +38123,7 @@
       </c>
       <c r="C47" s="24" t="inlineStr">
         <is>
-          <t>JDB007（TH015）</t>
+          <t>验收数量</t>
         </is>
       </c>
       <c r="D47" s="27" t="inlineStr">
@@ -38120,7 +38138,7 @@
       </c>
       <c r="F47" s="28" t="inlineStr">
         <is>
-          <t>★ 精准命中：易助别名 accept_qty，易飞 TH015=验收数量</t>
+          <t>★ 精准命中（易助别名 accept_qty）</t>
         </is>
       </c>
     </row>
@@ -38137,22 +38155,22 @@
       </c>
       <c r="C48" s="25" t="inlineStr">
         <is>
-          <t>本币税前金额</t>
-        </is>
-      </c>
-      <c r="D48" s="29" t="inlineStr">
-        <is>
-          <t>TH047</t>
-        </is>
-      </c>
-      <c r="E48" s="29" t="inlineStr">
-        <is>
-          <t>需换列</t>
+          <t>本币税前 / 原币税前</t>
+        </is>
+      </c>
+      <c r="D48" s="27" t="inlineStr">
+        <is>
+          <t>TH047 / TH045</t>
+        </is>
+      </c>
+      <c r="E48" s="27" t="inlineStr">
+        <is>
+          <t>直接对应</t>
         </is>
       </c>
       <c r="F48" s="28" t="inlineStr">
         <is>
-          <t>⚠ 实测 TH047(本币税前 2569.49) ≠ TH019(原币进货金额 400)。金额口径需确认本币/原币/含税</t>
+          <t>★★ 用户裁决：TH047=本币，TH045=原币。实测单号 26051600001：TH045=353.98(原币) TH047=2569.49(本币)</t>
         </is>
       </c>
     </row>
@@ -38169,7 +38187,7 @@
       </c>
       <c r="C49" s="24" t="inlineStr">
         <is>
-          <t>QKA001（TA001）</t>
+          <t>品号</t>
         </is>
       </c>
       <c r="D49" s="27" t="inlineStr">
@@ -38201,7 +38219,7 @@
       </c>
       <c r="C50" s="25" t="inlineStr">
         <is>
-          <t>QKA002（TA002）</t>
+          <t>年月</t>
         </is>
       </c>
       <c r="D50" s="27" t="inlineStr">
@@ -38233,7 +38251,7 @@
       </c>
       <c r="C51" s="24" t="inlineStr">
         <is>
-          <t>QKA004（TA004）</t>
+          <t>工单单号</t>
         </is>
       </c>
       <c r="D51" s="27" t="inlineStr">
@@ -38248,7 +38266,7 @@
       </c>
       <c r="F51" s="28" t="inlineStr">
         <is>
-          <t>易飞 TA003=工单单别 TA004=工单单号</t>
+          <t>直接对应</t>
         </is>
       </c>
     </row>
@@ -38265,7 +38283,7 @@
       </c>
       <c r="C52" s="25" t="inlineStr">
         <is>
-          <t>QKA005（TA012）</t>
+          <t>生产入库</t>
         </is>
       </c>
       <c r="D52" s="27" t="inlineStr">
@@ -38297,7 +38315,7 @@
       </c>
       <c r="C53" s="24" t="inlineStr">
         <is>
-          <t>QKA006（TA015）</t>
+          <t>本期投入材料成本</t>
         </is>
       </c>
       <c r="D53" s="27" t="inlineStr">
@@ -38329,7 +38347,7 @@
       </c>
       <c r="C54" s="25" t="inlineStr">
         <is>
-          <t>QKA007（TA016）</t>
+          <t>本期投入人工成本</t>
         </is>
       </c>
       <c r="D54" s="27" t="inlineStr">
@@ -38344,7 +38362,7 @@
       </c>
       <c r="F54" s="28" t="inlineStr">
         <is>
-          <t>直接对应。实测少量非零</t>
+          <t>直接对应</t>
         </is>
       </c>
     </row>
@@ -38361,7 +38379,7 @@
       </c>
       <c r="C55" s="24" t="inlineStr">
         <is>
-          <t>QKA008（TA017）</t>
+          <t>本期投入制造费用</t>
         </is>
       </c>
       <c r="D55" s="27" t="inlineStr">
@@ -38376,7 +38394,7 @@
       </c>
       <c r="F55" s="28" t="inlineStr">
         <is>
-          <t>直接对应。实测少量非零</t>
+          <t>直接对应</t>
         </is>
       </c>
     </row>
@@ -38396,19 +38414,19 @@
           <t>本期投入加工费用</t>
         </is>
       </c>
-      <c r="D56" s="29" t="inlineStr">
+      <c r="D56" s="27" t="inlineStr">
         <is>
           <t>TA018</t>
         </is>
       </c>
-      <c r="E56" s="29" t="inlineStr">
-        <is>
-          <t>需换列</t>
+      <c r="E56" s="27" t="inlineStr">
+        <is>
+          <t>直接对应</t>
         </is>
       </c>
       <c r="F56" s="28" t="inlineStr">
         <is>
-          <t>⚠ 易助=委外成本；易飞=加工费用，无独立委外列。实测有值</t>
+          <t>★ 易飞口径=加工费用（含委外），与 INVLC.LC029 同构</t>
         </is>
       </c>
     </row>
@@ -38425,7 +38443,7 @@
       </c>
       <c r="C57" s="24" t="inlineStr">
         <is>
-          <t>HDA001（TC002）</t>
+          <t>采购单号</t>
         </is>
       </c>
       <c r="D57" s="27" t="inlineStr">
@@ -38457,7 +38475,7 @@
       </c>
       <c r="C58" s="25" t="inlineStr">
         <is>
-          <t>HDA003（TC003）</t>
+          <t>采购日期</t>
         </is>
       </c>
       <c r="D58" s="27" t="inlineStr">
@@ -38489,7 +38507,7 @@
       </c>
       <c r="C59" s="24" t="inlineStr">
         <is>
-          <t>HDA004（TC004）</t>
+          <t>供应商</t>
         </is>
       </c>
       <c r="D59" s="27" t="inlineStr">
@@ -38504,7 +38522,7 @@
       </c>
       <c r="F59" s="28" t="inlineStr">
         <is>
-          <t>直接对应（易助别名 supplier）</t>
+          <t>直接对应</t>
         </is>
       </c>
     </row>
@@ -38521,7 +38539,7 @@
       </c>
       <c r="C60" s="25" t="inlineStr">
         <is>
-          <t>HDA021（TC014）</t>
+          <t>审核码</t>
         </is>
       </c>
       <c r="D60" s="27" t="inlineStr">
@@ -38536,7 +38554,7 @@
       </c>
       <c r="F60" s="28" t="inlineStr">
         <is>
-          <t>Y(281)/N(168)/V(14)</t>
+          <t>V=作废，只取 ='Y'（实测 Y281/N168/V14）</t>
         </is>
       </c>
     </row>
@@ -38553,7 +38571,7 @@
       </c>
       <c r="C61" s="24" t="inlineStr">
         <is>
-          <t>HDB001（TD002）</t>
+          <t>采购单号</t>
         </is>
       </c>
       <c r="D61" s="27" t="inlineStr">
@@ -38585,7 +38603,7 @@
       </c>
       <c r="C62" s="25" t="inlineStr">
         <is>
-          <t>HDB003（TD004）</t>
+          <t>品号</t>
         </is>
       </c>
       <c r="D62" s="27" t="inlineStr">
@@ -38617,7 +38635,7 @@
       </c>
       <c r="C63" s="24" t="inlineStr">
         <is>
-          <t>HDB006（TD008）</t>
+          <t>采购数量</t>
         </is>
       </c>
       <c r="D63" s="27" t="inlineStr">
@@ -38649,7 +38667,7 @@
       </c>
       <c r="C64" s="25" t="inlineStr">
         <is>
-          <t>HDB009（TD011）</t>
+          <t>采购金额</t>
         </is>
       </c>
       <c r="D64" s="27" t="inlineStr">
@@ -38664,7 +38682,7 @@
       </c>
       <c r="F64" s="28" t="inlineStr">
         <is>
-          <t>直接对应（易飞 TD011=采购金额，实测有值）</t>
+          <t>直接对应。实测有值</t>
         </is>
       </c>
     </row>
@@ -38681,7 +38699,7 @@
       </c>
       <c r="C65" s="24" t="inlineStr">
         <is>
-          <t>NFA001（LE001）</t>
+          <t>会计科目</t>
         </is>
       </c>
       <c r="D65" s="27" t="inlineStr">
@@ -38713,7 +38731,7 @@
       </c>
       <c r="C66" s="25" t="inlineStr">
         <is>
-          <t>NFA002（LE002）</t>
+          <t>会计年度</t>
         </is>
       </c>
       <c r="D66" s="27" t="inlineStr">
@@ -38728,7 +38746,7 @@
       </c>
       <c r="F66" s="28" t="inlineStr">
         <is>
-          <t>实测 4 位(2026)。易助 NFA002=year</t>
+          <t>实测 4 位（2026）</t>
         </is>
       </c>
     </row>
@@ -38745,7 +38763,7 @@
       </c>
       <c r="C67" s="24" t="inlineStr">
         <is>
-          <t>NFA003（LE003）</t>
+          <t>期间</t>
         </is>
       </c>
       <c r="D67" s="27" t="inlineStr">
@@ -38760,7 +38778,7 @@
       </c>
       <c r="F67" s="28" t="inlineStr">
         <is>
-          <t>实测 2 位(04)。易助 NFA003=month</t>
+          <t>实测 2 位（04）</t>
         </is>
       </c>
     </row>
@@ -38777,7 +38795,7 @@
       </c>
       <c r="C68" s="25" t="inlineStr">
         <is>
-          <t>NFA011（LE014）</t>
+          <t>借方本币</t>
         </is>
       </c>
       <c r="D68" s="27" t="inlineStr">
@@ -38792,7 +38810,7 @@
       </c>
       <c r="F68" s="28" t="inlineStr">
         <is>
-          <t>直接对应。实测有值(LE013 借方原币=LE014 借方本币)</t>
+          <t>直接对应</t>
         </is>
       </c>
     </row>
@@ -38809,7 +38827,7 @@
       </c>
       <c r="C69" s="24" t="inlineStr">
         <is>
-          <t>NFA012（LE017）</t>
+          <t>贷方本币</t>
         </is>
       </c>
       <c r="D69" s="27" t="inlineStr">
@@ -38824,7 +38842,7 @@
       </c>
       <c r="F69" s="28" t="inlineStr">
         <is>
-          <t>直接对应。实测有值</t>
+          <t>直接对应</t>
         </is>
       </c>
     </row>
@@ -38841,7 +38859,7 @@
       </c>
       <c r="C70" s="25" t="inlineStr">
         <is>
-          <t>GCA003（LB005）</t>
+          <t>客户编号</t>
         </is>
       </c>
       <c r="D70" s="27" t="inlineStr">
@@ -38856,7 +38874,7 @@
       </c>
       <c r="F70" s="28" t="inlineStr">
         <is>
-          <t>直接对应。实测 LB005=客户编号(00WK/20241204)</t>
+          <t>直接对应</t>
         </is>
       </c>
     </row>
@@ -38873,7 +38891,7 @@
       </c>
       <c r="C71" s="24" t="inlineStr">
         <is>
-          <t>GCA004（LB004）</t>
+          <t>交易日期</t>
         </is>
       </c>
       <c r="D71" s="27" t="inlineStr">
@@ -38905,7 +38923,7 @@
       </c>
       <c r="C72" s="25" t="inlineStr">
         <is>
-          <t>GCA016（LB014）</t>
+          <t>本币金额</t>
         </is>
       </c>
       <c r="D72" s="27" t="inlineStr">
@@ -38937,7 +38955,7 @@
       </c>
       <c r="C73" s="24" t="inlineStr">
         <is>
-          <t>GCA017（LB016）</t>
+          <t>本币已核销金额</t>
         </is>
       </c>
       <c r="D73" s="27" t="inlineStr">
@@ -38952,7 +38970,7 @@
       </c>
       <c r="F73" s="28" t="inlineStr">
         <is>
-          <t>直接对应（易助=本币总计已冲）</t>
+          <t>直接对应</t>
         </is>
       </c>
     </row>
@@ -38969,7 +38987,7 @@
       </c>
       <c r="C74" s="25" t="inlineStr">
         <is>
-          <t>GCA020（LB011）</t>
+          <t>方向</t>
         </is>
       </c>
       <c r="D74" s="27" t="inlineStr">
@@ -38984,7 +39002,7 @@
       </c>
       <c r="F74" s="28" t="inlineStr">
         <is>
-          <t>★ 精准命中：易助 GCA020=1 增项；易飞 LB011 方向 numeric ±1，实测 1/-1 两值</t>
+          <t>★ 精准命中：numeric ±1，与 LNA015 同构</t>
         </is>
       </c>
     </row>
@@ -39001,7 +39019,7 @@
       </c>
       <c r="C75" s="24" t="inlineStr">
         <is>
-          <t>GDA003（TK003）</t>
+          <t>收款日期</t>
         </is>
       </c>
       <c r="D75" s="27" t="inlineStr">
@@ -39033,7 +39051,7 @@
       </c>
       <c r="C76" s="25" t="inlineStr">
         <is>
-          <t>GDA004（TK004）</t>
+          <t>客户编号</t>
         </is>
       </c>
       <c r="D76" s="27" t="inlineStr">
@@ -39065,7 +39083,7 @@
       </c>
       <c r="C77" s="24" t="inlineStr">
         <is>
-          <t>GDA013（TK033）</t>
+          <t>本币实收金额</t>
         </is>
       </c>
       <c r="D77" s="27" t="inlineStr">
@@ -39080,7 +39098,7 @@
       </c>
       <c r="F77" s="28" t="inlineStr">
         <is>
-          <t>直接对应（易助=本币收款）</t>
+          <t>直接对应</t>
         </is>
       </c>
     </row>
@@ -39097,7 +39115,7 @@
       </c>
       <c r="C78" s="25" t="inlineStr">
         <is>
-          <t>GDA022（TK020）</t>
+          <t>审核码</t>
         </is>
       </c>
       <c r="D78" s="27" t="inlineStr">
@@ -39112,7 +39130,7 @@
       </c>
       <c r="F78" s="28" t="inlineStr">
         <is>
-          <t>实测 Y(94)/N(53)/V(4)</t>
+          <t>V=作废，只取 ='Y'（实测 Y94/N53/V4）</t>
         </is>
       </c>
     </row>
@@ -39129,7 +39147,7 @@
       </c>
       <c r="C79" s="24" t="inlineStr">
         <is>
-          <t>GQA003（LB005）</t>
+          <t>应付对象编号</t>
         </is>
       </c>
       <c r="D79" s="27" t="inlineStr">
@@ -39161,7 +39179,7 @@
       </c>
       <c r="C80" s="25" t="inlineStr">
         <is>
-          <t>GQA004（LB004）</t>
+          <t>交易日期</t>
         </is>
       </c>
       <c r="D80" s="27" t="inlineStr">
@@ -39193,7 +39211,7 @@
       </c>
       <c r="C81" s="24" t="inlineStr">
         <is>
-          <t>GQA013（LB014）</t>
+          <t>本币金额</t>
         </is>
       </c>
       <c r="D81" s="27" t="inlineStr">
@@ -39225,7 +39243,7 @@
       </c>
       <c r="C82" s="25" t="inlineStr">
         <is>
-          <t>GQA022（LB011）</t>
+          <t>方向</t>
         </is>
       </c>
       <c r="D82" s="27" t="inlineStr">
@@ -39240,7 +39258,7 @@
       </c>
       <c r="F82" s="28" t="inlineStr">
         <is>
-          <t>同 GCA020，numeric ±1</t>
+          <t>numeric ±1</t>
         </is>
       </c>
     </row>
@@ -39257,7 +39275,7 @@
       </c>
       <c r="C83" s="24" t="inlineStr">
         <is>
-          <t>GPA003（TK004）</t>
+          <t>应付对象编号</t>
         </is>
       </c>
       <c r="D83" s="27" t="inlineStr">
@@ -39289,7 +39307,7 @@
       </c>
       <c r="C84" s="25" t="inlineStr">
         <is>
-          <t>GPA004（TK003）</t>
+          <t>付款日期</t>
         </is>
       </c>
       <c r="D84" s="27" t="inlineStr">
@@ -39321,12 +39339,12 @@
       </c>
       <c r="C85" s="24" t="inlineStr">
         <is>
-          <t>GPA016（LB014）</t>
+          <t>本币实付金额</t>
         </is>
       </c>
       <c r="D85" s="27" t="inlineStr">
         <is>
-          <t>LB014</t>
+          <t>TK031</t>
         </is>
       </c>
       <c r="E85" s="27" t="inlineStr">
@@ -39336,7 +39354,7 @@
       </c>
       <c r="F85" s="28" t="inlineStr">
         <is>
-          <t>⚠ 跨表：GPA016 语义同 GQA016，但 YSFGPA→ACPTK 单头无本币金额列。ACPTK.TK031=本币实付金额</t>
+          <t>直接对应（ACPTK 单头）</t>
         </is>
       </c>
     </row>
@@ -39353,12 +39371,12 @@
       </c>
       <c r="C86" s="25" t="inlineStr">
         <is>
-          <t>GPA017（(跨表)）</t>
+          <t>本币已核销金额</t>
         </is>
       </c>
       <c r="D86" s="27" t="inlineStr">
         <is>
-          <t>(跨表)</t>
+          <t>TK036</t>
         </is>
       </c>
       <c r="E86" s="27" t="inlineStr">
@@ -39368,7 +39386,7 @@
       </c>
       <c r="F86" s="28" t="inlineStr">
         <is>
-          <t>⚠ 同上，ACPTK 无异动台账列，核销类字段需改查 ACPLB</t>
+          <t>直接对应（ACPTK.TK036）</t>
         </is>
       </c>
     </row>
@@ -39400,7 +39418,7 @@
       </c>
       <c r="F87" s="28" t="inlineStr">
         <is>
-          <t>⚠ 同上，增减别在 ACPTK 无对应列</t>
+          <t>⚠ ACPTK 单头无『增减别』列。易飞做法：异动台账查 ACPLB.LB011，单头查 ACPTK。需按模板口径二选一</t>
         </is>
       </c>
     </row>
@@ -39420,193 +39438,238 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7"/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" style="3" min="1" max="1"/>
-    <col width="24" customWidth="1" style="3" min="2" max="2"/>
-    <col width="28" customWidth="1" style="3" min="3" max="3"/>
-    <col width="14" customWidth="1" style="3" min="4" max="4"/>
-    <col width="36" customWidth="1" style="3" min="5" max="5"/>
+    <col width="16" customWidth="1" style="3" min="1" max="1"/>
+    <col width="34" customWidth="1" style="3" min="2" max="2"/>
+    <col width="24" customWidth="1" style="3" min="3" max="3"/>
+    <col width="30" customWidth="1" style="3" min="4" max="4"/>
+    <col width="10" customWidth="1" style="3" min="5" max="5"/>
+    <col width="76" customWidth="1" style="3" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.8" customHeight="1" s="3">
-      <c r="A1" s="16" t="inlineStr">
-        <is>
-          <t>易助专有常量（改写时必须同步调整，不属于表名映射）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16.2" customHeight="1" s="3">
-      <c r="A2" s="18" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="31" t="inlineStr">
         <is>
           <t>项目</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B1" s="31" t="inlineStr">
         <is>
           <t>出现位置</t>
         </is>
       </c>
-      <c r="C2" s="18" t="inlineStr">
+      <c r="C1" s="31" t="inlineStr">
         <is>
           <t>易助取值</t>
         </is>
       </c>
-      <c r="D2" s="18" t="inlineStr">
+      <c r="D1" s="31" t="inlineStr">
         <is>
           <t>易飞取值</t>
         </is>
       </c>
-      <c r="E2" s="18" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1" s="3">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="E1" s="31" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="F1" s="31" t="inlineStr">
+        <is>
+          <t>说明 / 实测证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="62" customHeight="1" s="3">
+      <c r="A2" s="33" t="inlineStr">
         <is>
           <t>审核码</t>
         </is>
       </c>
-      <c r="B3" s="20" t="inlineStr">
-        <is>
-          <t>JSKKEA.KEA040 等</t>
-        </is>
-      </c>
-      <c r="C3" s="20" t="inlineStr">
-        <is>
-          <t>T=已审核 / F=未审核</t>
-        </is>
-      </c>
-      <c r="D3" s="21" t="inlineStr">
-        <is>
-          <t>Y=已审核 / N=未审核</t>
-        </is>
-      </c>
-      <c r="E3" s="20" t="inlineStr">
-        <is>
-          <t>易飞审核码取值待确认</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1" s="3">
-      <c r="A4" s="22" t="inlineStr">
+      <c r="B2" s="33" t="inlineStr">
+        <is>
+          <t>JSKKEA.KEA040 / KEB021 / JDA026 / HDA021 / GDA022 等 9 处</t>
+        </is>
+      </c>
+      <c r="C2" s="33" t="inlineStr">
+        <is>
+          <t>T=已审核</t>
+        </is>
+      </c>
+      <c r="D2" s="33" t="inlineStr">
+        <is>
+          <t>Y=已审核 / N=未审核 / V=作废</t>
+        </is>
+      </c>
+      <c r="E2" s="33" t="inlineStr">
+        <is>
+          <t>已裁决</t>
+        </is>
+      </c>
+      <c r="F2" s="33" t="inlineStr">
+        <is>
+          <t>★ 用户裁决：V=作废，统计只筛 ='Y'。实测各表均为 Y/N/V 三值（ACRTK Y94/N53/V4、ACPTK Y79/N122/V18/U1、PURTG Y192/N108/V2、PURTC Y281/N168/V14）。→ 模板默认值由 'T' 改为 'Y'，不含 V</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="62" customHeight="1" s="3">
+      <c r="A3" s="33" t="inlineStr">
         <is>
           <t>单据类型码</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B3" s="33" t="inlineStr">
         <is>
           <t>JSKLNA.LNA001</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="C3" s="33" t="inlineStr">
         <is>
           <t>33=销货, 84/85=生产耗用</t>
         </is>
       </c>
-      <c r="D4" s="21" t="inlineStr">
-        <is>
-          <t>易飞直接通过单别字段关联</t>
-        </is>
-      </c>
-      <c r="E4" s="23" t="inlineStr">
-        <is>
-          <t>易飞是否有等价单别码待确认</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1" s="3">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>出库标志</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr">
-        <is>
-          <t>JSKLNA.LNA004</t>
-        </is>
-      </c>
-      <c r="C5" s="20" t="inlineStr">
-        <is>
-          <t>O=出库</t>
-        </is>
-      </c>
-      <c r="D5" s="21" t="inlineStr"/>
-      <c r="E5" s="20" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1" s="3">
-      <c r="A6" s="22" t="inlineStr">
-        <is>
-          <t>本币成本</t>
-        </is>
-      </c>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t>JSKLNA.LNA013</t>
-        </is>
-      </c>
-      <c r="C6" s="23" t="inlineStr">
-        <is>
-          <t>本币成本金额</t>
-        </is>
-      </c>
-      <c r="D6" s="21" t="inlineStr"/>
-      <c r="E6" s="23" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1" s="3">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="D3" s="33" t="inlineStr">
+        <is>
+          <t>CMSMQ.MQ003（经 LA006 关联 MQ001）</t>
+        </is>
+      </c>
+      <c r="E3" s="33" t="inlineStr">
+        <is>
+          <t>已裁决</t>
+        </is>
+      </c>
+      <c r="F3" s="33" t="inlineStr">
+        <is>
+          <t>★★ 用户裁决：LA006=单别，一种单据可有多个单别，单别+单号=唯一 key；LA006 关联 CMSMQ.MQ001，MQ003=具体单据类型（char(2)）。实测 INVLA 出现的单别 100% 可关联成功 → 不硬编码单别码，走 CMSMQ 关联</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="62" customHeight="1" s="3">
+      <c r="A4" s="33" t="inlineStr">
+        <is>
+          <t>出入库标志</t>
+        </is>
+      </c>
+      <c r="B4" s="33" t="inlineStr">
+        <is>
+          <t>JSKLNA.LNA004 + LNA015</t>
+        </is>
+      </c>
+      <c r="C4" s="33" t="inlineStr">
+        <is>
+          <t>LNA004='I'/'O'；LNA015=±1 加减项</t>
+        </is>
+      </c>
+      <c r="D4" s="33" t="inlineStr">
+        <is>
+          <t>LA005 入出别 numeric ±1</t>
+        </is>
+      </c>
+      <c r="E4" s="33" t="inlineStr">
+        <is>
+          <t>已裁决</t>
+        </is>
+      </c>
+      <c r="F4" s="33" t="inlineStr">
+        <is>
+          <t>★ 易飞用单一列 LA005 同时表达方向与符号（实测 1:1174 行 / -1:1158 行）。→ SQL 去掉 LNA015 乘数，改乘 LA005；不再需要 LNA004</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="62" customHeight="1" s="3">
+      <c r="A5" s="33" t="inlineStr">
+        <is>
+          <t>本币/原币口径</t>
+        </is>
+      </c>
+      <c r="B5" s="33" t="inlineStr">
+        <is>
+          <t>JSKJDB.JDB010 等金额字段</t>
+        </is>
+      </c>
+      <c r="C5" s="33" t="inlineStr">
+        <is>
+          <t>本币</t>
+        </is>
+      </c>
+      <c r="D5" s="33" t="inlineStr">
+        <is>
+          <t>TH047=本币税前 / TH045=原币税前</t>
+        </is>
+      </c>
+      <c r="E5" s="33" t="inlineStr">
+        <is>
+          <t>已裁决</t>
+        </is>
+      </c>
+      <c r="F5" s="33" t="inlineStr">
+        <is>
+          <t>★★ 用户裁决。实测单号 26051600001：TH045=353.98(原币) / TH047=2569.49(本币) / TH046=46.02 / TH048=334.03。TH019=原币进货金额(400) 是另一个口径，勿混用</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="62" customHeight="1" s="3">
+      <c r="A6" s="33" t="inlineStr">
         <is>
           <t>人工/制造/委外</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>JSKLNA.LNA035/036/037</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>易助特有三列</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr">
-        <is>
-          <t>易飞是否存在等价列—— 关键风险点</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1" s="3">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="C6" s="33" t="inlineStr">
+        <is>
+          <t>人工 / 制造费用 / 委外成本</t>
+        </is>
+      </c>
+      <c r="D6" s="33" t="inlineStr">
+        <is>
+          <t>LA018 金额-人工 / LA019 金额-制费 / LA020 金额-加工</t>
+        </is>
+      </c>
+      <c r="E6" s="33" t="inlineStr">
+        <is>
+          <t>已裁决</t>
+        </is>
+      </c>
+      <c r="F6" s="33" t="inlineStr">
+        <is>
+          <t>★ 此前担心的『易助特有列』不成立。实测非零行：LA018=174 / LA019=174 / LA020=229。★ 易飞口径中『加工费用』含委外 —— 与 CSTTA.TA018、INVLC.LC029 同构，全线一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="62" customHeight="1" s="3">
+      <c r="A7" s="33" t="inlineStr">
         <is>
           <t>成本四要素</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>SGMQKA.QKA006~009</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
-        <is>
-          <t>材料/人工/制造/委外</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr"/>
-      <c r="E8" s="23" t="inlineStr">
-        <is>
-          <t>待确认</t>
+      <c r="C7" s="33" t="inlineStr">
+        <is>
+          <t>材料 / 人工 / 制造 / 委外</t>
+        </is>
+      </c>
+      <c r="D7" s="33" t="inlineStr">
+        <is>
+          <t>CSTTA.TA015/016/017/018 + INVLC.LC026/027/028/029</t>
+        </is>
+      </c>
+      <c r="E7" s="33" t="inlineStr">
+        <is>
+          <t>已裁决</t>
+        </is>
+      </c>
+      <c r="F7" s="33" t="inlineStr">
+        <is>
+          <t>两处四要素均齐备。★ 注意：四要素不可加进期末成本公式（实测加进去仅 88/141 吻合），仅作成本构成维度使用</t>
         </is>
       </c>
     </row>
@@ -39621,17 +39684,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="3" min="1" max="1"/>
-    <col width="24" customWidth="1" style="3" min="2" max="2"/>
-    <col width="16" customWidth="1" style="3" min="3" max="3"/>
-    <col width="24" customWidth="1" style="3" min="4" max="4"/>
-    <col width="40" customWidth="1" style="3" min="5" max="5"/>
-    <col width="62" customWidth="1" style="3" min="6" max="6"/>
-    <col width="52" customWidth="1" style="3" min="7" max="7"/>
-    <col width="44" customWidth="1" style="3" min="8" max="8"/>
+    <col width="22" customWidth="1" style="3" min="2" max="2"/>
+    <col width="18" customWidth="1" style="3" min="3" max="3"/>
+    <col width="30" customWidth="1" style="3" min="4" max="4"/>
+    <col width="74" customWidth="1" style="3" min="5" max="5"/>
+    <col width="56" customWidth="1" style="3" min="6" max="6"/>
+    <col width="40" customWidth="1" style="3" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -39652,31 +39714,26 @@
       </c>
       <c r="D1" s="31" t="inlineStr">
         <is>
-          <t>易飞候选</t>
+          <t>现状</t>
         </is>
       </c>
       <c r="E1" s="31" t="inlineStr">
         <is>
-          <t>问题</t>
+          <t>实测证据 / 裁决依据</t>
         </is>
       </c>
       <c r="F1" s="31" t="inlineStr">
         <is>
-          <t>实测证据</t>
+          <t>建议方案</t>
         </is>
       </c>
       <c r="G1" s="31" t="inlineStr">
         <is>
-          <t>建议方案</t>
-        </is>
-      </c>
-      <c r="H1" s="31" t="inlineStr">
-        <is>
           <t>影响面</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="74" customHeight="1" s="3">
+    <row r="2" ht="96" customHeight="1" s="3">
       <c r="A2" s="32" t="inlineStr">
         <is>
           <t>P0</t>
@@ -39689,78 +39746,68 @@
       </c>
       <c r="C2" s="33" t="inlineStr">
         <is>
-          <t>期末成本</t>
+          <t>仓库级期末成本</t>
         </is>
       </c>
       <c r="D2" s="33" t="inlineStr">
         <is>
-          <t>INVML / INVLN</t>
+          <t>用户已确认 INVML / INVLE『只有数量没有成本』</t>
         </is>
       </c>
       <c r="E2" s="33" t="inlineStr">
         <is>
-          <t>INVML 无任何成本列；INVLN 有 LN005 月初总成本但无仓库维度</t>
+          <t>实测 INVLE 48 个业务列中，成本列 LE007/LE009/LE011/LE013/LE015/LE017/LE019/LE021/LE023/LE025/LE027 及四要素 LE028~LE031 全部恒为 0；INVML.MC008 不存在，ML012 是 0/1 标志位（0:649行/1:346行）不是成本。INV2-003.SDD 官方定义确认这些列名虽为『预留字段』但备注写的是『月初成本/本月入库金额』—— 即设计上未启用</t>
         </is>
       </c>
       <c r="F2" s="33" t="inlineStr">
         <is>
-          <t>实测 INVML 1019 行，ML005 库存数量非零 341 行、ML012 非零 346 行（字典无中文名，疑为成本）；ML007/ML013~ML017 全零。INVLN 0 行空表</t>
+          <t>① 仓库级期末成本改由 INVLC 按品号+仓库汇总（INVLC 有完整成本列 LC005~LC025）—— 可行② 批号级成本无法还原，inventory_by_batch 模板需降级为仅数量或明确标注成本缺失</t>
         </is>
       </c>
       <c r="G2" s="33" t="inlineStr">
         <is>
-          <t>① 确认 ML012 是否即库存金额（可解 INVML 成本缺口）② LPB005 改由 ML012 或 INVMC.MC008 派生 ③ 或放弃仓库级期末成本，只做品号级</t>
-        </is>
-      </c>
-      <c r="H2" s="33" t="inlineStr">
-        <is>
-          <t>阻塞 4 个模板：inventory_asof / inventory_asof_by_item / inventory_asof_by_warehouse / inventory_by_batch</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="74" customHeight="1" s="3">
-      <c r="A3" s="32" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>inventory_asof / inventory_asof_by_warehouse / inventory_by_batch 三个模板</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="96" customHeight="1" s="3">
+      <c r="A3" s="34" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="B3" s="33" t="inlineStr">
         <is>
-          <t>JSKLNA.LNA018</t>
+          <t>JSKKEB.KEB011</t>
         </is>
       </c>
       <c r="C3" s="33" t="inlineStr">
         <is>
-          <t>销货客户</t>
+          <t>过滤字段（&gt;0）</t>
         </is>
       </c>
       <c r="D3" s="33" t="inlineStr">
         <is>
-          <t>INVLA.LA024?</t>
+          <t>仍待确认过滤意图</t>
         </is>
       </c>
       <c r="E3" s="33" t="inlineStr">
         <is>
-          <t>易飞 LA024『对象』语义混杂，不能直接用</t>
+          <t>templates.ts:281 `WHERE KEB021 = :approve_status AND KEB011 &gt; 0`（与审核码并列使用）。易飞 COPTH 无『已交量/已出货量』列；最接近 TH008 数量、TH042 已开票数量</t>
         </is>
       </c>
       <c r="F3" s="33" t="inlineStr">
         <is>
-          <t>实测 LA024 三类值：客户名（'天之蓝海更蓝'）、供应商名（'第一波供应商'）、关联单号（'5102-20260920002'）</t>
+          <t>① 若原意仅是排除赠品/零行 → 改用 TH008 &gt; 0② 若原意是『实际已交量』→ 易飞无等价列，需改用 TH008 或去掉该过滤</t>
         </is>
       </c>
       <c r="G3" s="33" t="inlineStr">
         <is>
-          <t>改 JOIN COPTG.TG004（客户编号）取客户；INVLA 按 LA006 单别 + LA007 单号 关联 COPTG</t>
-        </is>
-      </c>
-      <c r="H3" s="33" t="inlineStr">
-        <is>
-          <t>影响 gross_profit_by_customer 毛利下钻模板</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="74" customHeight="1" s="3">
+          <t>revenue_by_product 收入聚合</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="96" customHeight="1" s="3">
       <c r="A4" s="34" t="inlineStr">
         <is>
           <t>P1</t>
@@ -39768,294 +39815,36 @@
       </c>
       <c r="B4" s="33" t="inlineStr">
         <is>
-          <t>JSKKEB.KEB011</t>
+          <t>YSFGPA.GPA020</t>
         </is>
       </c>
       <c r="C4" s="33" t="inlineStr">
         <is>
-          <t>过滤字段（&gt;0）</t>
+          <t>应付增减别</t>
         </is>
       </c>
       <c r="D4" s="33" t="inlineStr">
         <is>
-          <t>COPTH.TH008?</t>
+          <t>ACPTK 单头无对应列</t>
         </is>
       </c>
       <c r="E4" s="33" t="inlineStr">
         <is>
-          <t>易助用 KEB011&gt;0 作过滤条件，易飞无『已交量/已出货量』列</t>
+          <t>实测 ACPTK（付款单主档）无『方向/增减别』列；而 ACPLB（应付异动档）LB011 才是 numeric ±1。两张表语义分工：ACPTK=单据、ACPLB=异动台账</t>
         </is>
       </c>
       <c r="F4" s="33" t="inlineStr">
         <is>
-          <t>templates.ts:281 `WHERE KEB021 = :approve_status AND KEB011 &gt; 0`；易飞 COPTH.TH008=数量、TH042=已开票数量</t>
+          <t>① 若模板口径是『应付异动余额』→ 应改查 ACPLB（与 YSFGQA.GQA020 同源）② 若口径是『付款单头』→ 去掉该过滤条件</t>
         </is>
       </c>
       <c r="G4" s="33" t="inlineStr">
         <is>
-          <t>① 确认过滤意图（是否仅为排除赠品/零行）② 若为已交量，易飞需改用 TH008 或删过滤</t>
-        </is>
-      </c>
-      <c r="H4" s="33" t="inlineStr">
-        <is>
-          <t>影响 revenue_by_product 收入聚合模板</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="74" customHeight="1" s="3">
-      <c r="A5" s="34" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="B5" s="33" t="inlineStr">
-        <is>
-          <t>JSKLPA.LPA003/LPA004</t>
-        </is>
-      </c>
-      <c r="C5" s="33" t="inlineStr">
-        <is>
-          <t>期末数量/成本</t>
-        </is>
-      </c>
-      <c r="D5" s="33" t="inlineStr">
-        <is>
-          <t>INVLB.LB003/LB004</t>
-        </is>
-      </c>
-      <c r="E5" s="33" t="inlineStr">
-        <is>
-          <t>易飞 INVLB 只有『月初』列，无期末列（与用户备注一致）</t>
-        </is>
-      </c>
-      <c r="F5" s="33" t="inlineStr">
-        <is>
-          <t>实测 LB003=月初总数量、LB004=月初总成本、LB010=单位成本；最新年月 202506 仅 7 行</t>
-        </is>
-      </c>
-      <c r="G5" s="33" t="inlineStr">
-        <is>
-          <t>视图层计算：期末 = 月初(LB003) + SUM(INVLA.LA005 × LA011) 期间异动净额。成本同理用 LA013</t>
-        </is>
-      </c>
-      <c r="H5" s="33" t="inlineStr">
-        <is>
-          <t>影响 period_comparison 期间对比 + avg_unit_cost 平均单位成本</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="74" customHeight="1" s="3">
-      <c r="A6" s="34" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="B6" s="33" t="inlineStr">
-        <is>
-          <t>JSKLNA.LNA001</t>
-        </is>
-      </c>
-      <c r="C6" s="33" t="inlineStr">
-        <is>
-          <t>单据类型码</t>
-        </is>
-      </c>
-      <c r="D6" s="33" t="inlineStr">
-        <is>
-          <t>INVLA.LA006</t>
-        </is>
-      </c>
-      <c r="E6" s="33" t="inlineStr">
-        <is>
-          <t>易助是数字码（'33'销货/'82'领料），易飞是单别 char(4)</t>
-        </is>
-      </c>
-      <c r="F6" s="33" t="inlineStr">
-        <is>
-          <t>实测 LA006 有 130+ 种单别值：2301/2302/023w/5401/5501/TZ01/XX01…</t>
-        </is>
-      </c>
-      <c r="G6" s="33" t="inlineStr">
-        <is>
-          <t>建单别码对照表（视图层或配置层），把易飞单别映射到业务类别：销货/领料/进货/调整</t>
-        </is>
-      </c>
-      <c r="H6" s="33" t="inlineStr">
-        <is>
-          <t>阻塞 gross_profit 成本口径 —— 必须同时锁定单别 + 入出别（对应原 LNA001+LNA004 双条件）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="74" customHeight="1" s="3">
-      <c r="A7" s="34" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="B7" s="33" t="inlineStr">
-        <is>
-          <t>JSKKEA.KEA023 / JSKKEB.KEB012</t>
-        </is>
-      </c>
-      <c r="C7" s="33" t="inlineStr">
-        <is>
-          <t>收入（无税）</t>
-        </is>
-      </c>
-      <c r="D7" s="33" t="inlineStr">
-        <is>
-          <t>COPTG.TG045 / COPTH.TH037</t>
-        </is>
-      </c>
-      <c r="E7" s="33" t="inlineStr">
-        <is>
-          <t>易飞同名『金额』列是含税，易助要的是无税收入</t>
-        </is>
-      </c>
-      <c r="F7" s="33" t="inlineStr">
-        <is>
-          <t>实测单号 20260911001：TG045 本币销货金额 10176.99（含税）、TG046 税额 1323.01、TG045-TG046=8853.98（无税）；COPTH.TH013 金额 10000（含税）、TH037 本币税前 8849.56</t>
-        </is>
-      </c>
-      <c r="G7" s="33" t="inlineStr">
-        <is>
-          <t>收入口径改为 TG045-TG046（单头）或 TH037（单身），不要用 TH013/TG045 原值</t>
-        </is>
-      </c>
-      <c r="H7" s="33" t="inlineStr">
-        <is>
-          <t>影响 gross_profit 毛利率 —— 分子分母口径必须一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="74" customHeight="1" s="3">
-      <c r="A8" s="35" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B8" s="33" t="inlineStr">
-        <is>
-          <t>JSKLNA.LNA037 / SGMQKA.QKA009</t>
-        </is>
-      </c>
-      <c r="C8" s="33" t="inlineStr">
-        <is>
-          <t>委外成本</t>
-        </is>
-      </c>
-      <c r="D8" s="33" t="inlineStr">
-        <is>
-          <t>INVLA.LA020 / CSTTA.TA018</t>
-        </is>
-      </c>
-      <c r="E8" s="33" t="inlineStr">
-        <is>
-          <t>易飞无独立『委外』列，归入『加工费用』</t>
-        </is>
-      </c>
-      <c r="F8" s="33" t="inlineStr">
-        <is>
-          <t>实测 INVLA.LA020 金额-加工 229 行非零；CSTTA.TA018 本期投入加工费用有值。相邻列 LA018 人工(174) LA019 制费(174) 均有值</t>
-        </is>
-      </c>
-      <c r="G8" s="33" t="inlineStr">
-        <is>
-          <t>与业务确认：委外加工是否 = 加工费用？若是则直接映射；若需拆分则无法从现有列还原</t>
-        </is>
-      </c>
-      <c r="H8" s="33" t="inlineStr">
-        <is>
-          <t>影响 mfg_cost_breakdown 制费成本拆解</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="74" customHeight="1" s="3">
-      <c r="A9" s="35" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B9" s="33" t="inlineStr">
-        <is>
-          <t>JSKJDB.JDB010</t>
-        </is>
-      </c>
-      <c r="C9" s="33" t="inlineStr">
-        <is>
-          <t>进货金额</t>
-        </is>
-      </c>
-      <c r="D9" s="33" t="inlineStr">
-        <is>
-          <t>PURTH.TH047 / TH019</t>
-        </is>
-      </c>
-      <c r="E9" s="33" t="inlineStr">
-        <is>
-          <t>本币/原币口径不明</t>
-        </is>
-      </c>
-      <c r="F9" s="33" t="inlineStr">
-        <is>
-          <t>实测单号 26051600001：TH019 原币进货金额 400、TH047 本币税前 2569.49、TH048 本币税额 334.03</t>
-        </is>
-      </c>
-      <c r="G9" s="33" t="inlineStr">
-        <is>
-          <t>确认 JDB010 口径（本币税前 / 原币 / 含税），三者差异巨大</t>
-        </is>
-      </c>
-      <c r="H9" s="33" t="inlineStr">
-        <is>
-          <t>影响采购金额类模板</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="74" customHeight="1" s="3">
-      <c r="A10" s="35" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B10" s="33" t="inlineStr">
-        <is>
-          <t>全部审核码字段</t>
-        </is>
-      </c>
-      <c r="C10" s="33" t="inlineStr">
-        <is>
-          <t>审核码</t>
-        </is>
-      </c>
-      <c r="D10" s="33" t="inlineStr">
-        <is>
-          <t>各表 *审核码</t>
-        </is>
-      </c>
-      <c r="E10" s="33" t="inlineStr">
-        <is>
-          <t>易助仅 'T'，易飞实测 Y/N/V 三值</t>
-        </is>
-      </c>
-      <c r="F10" s="33" t="inlineStr">
-        <is>
-          <t>实测：ACRTK Y94/N53/V4、ACPTK Y79/N122/V18/U1、PURTG Y192/N108/V2、PURTC Y281/N168/V14、PURTH Y378/N164、COPTH/PURTD 同样三值</t>
-        </is>
-      </c>
-      <c r="G10" s="33" t="inlineStr">
-        <is>
-          <t>① 确认 V 含义（作废？未确认？）② 模板默认值从 'T' 改为 'Y' ③ 是否需要排除 V</t>
-        </is>
-      </c>
-      <c r="H10" s="33" t="inlineStr">
-        <is>
-          <t>影响所有带审核码过滤的模板（易助 20 个模板中 9 个用审核码）</t>
+          <t>应付余额类模板（payable_balance）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/plans/analysis-table-mapping.xlsx
+++ b/docs/plans/analysis-table-mapping.xlsx
@@ -11,7 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="候选总表" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段需求" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="专有常量" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待裁决项" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MQ003单据性质" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待裁决项" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'候选总表'!$A$2:$F$1176</definedName>
@@ -272,7 +273,7 @@
       <color rgb="0001579B"/>
     </font>
   </fonts>
-  <fills count="45">
+  <fills count="46">
     <fill>
       <patternFill/>
     </fill>
@@ -524,6 +525,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E3F2FD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -817,7 +823,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -911,6 +917,12 @@
     </xf>
     <xf numFmtId="0" fontId="37" fillId="43" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="37" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="45" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -37136,17 +37148,17 @@
       </c>
       <c r="D16" s="30" t="inlineStr">
         <is>
-          <t>(需跨表)</t>
+          <t>(降级:仅数量)</t>
         </is>
       </c>
       <c r="E16" s="30" t="inlineStr">
         <is>
-          <t>无等价列</t>
+          <t>已降级</t>
         </is>
       </c>
       <c r="F16" s="28" t="inlineStr">
         <is>
-          <t>⚠ P0 仍在：用户已确认 INVLE/INVML 均『只有数量没有成本』（实测 LE007~LE031 全零）。仓库级期末成本只能由 INVLC.MC008 口径或 INVLA.LA013 汇总派生，批号级成本不可还原</t>
+          <t>★ 用户裁决 2026-10-09：inventory_by_batch 模板降级为仅数量。实测 INVLE 无成本列（LE007~LE027 及四要素 371 行全零），批号级成本不可还原。仓库级成本可由 INVLC 公式汇总，不受影响</t>
         </is>
       </c>
     </row>
@@ -37838,19 +37850,19 @@
           <t>数量</t>
         </is>
       </c>
-      <c r="D38" s="30" t="inlineStr">
-        <is>
-          <t>TH008?</t>
-        </is>
-      </c>
-      <c r="E38" s="30" t="inlineStr">
-        <is>
-          <t>无等价列</t>
+      <c r="D38" s="29" t="inlineStr">
+        <is>
+          <t>TH008 &gt; 0</t>
+        </is>
+      </c>
+      <c r="E38" s="29" t="inlineStr">
+        <is>
+          <t>需换列</t>
         </is>
       </c>
       <c r="F38" s="28" t="inlineStr">
         <is>
-          <t>⚠ 易助用 KEB011&gt;0 作过滤条件（与审核码并列）。易飞无『已交量』列，最接近 TH008 数量。需确认过滤意图</t>
+          <t>★ 用户裁决：过滤意图=『实际已交量』。易飞 COPTH 无同名列，最接近 TH008 数量。落地：WHERE TH008 &gt; 0，并在视图列注释标注口径差异</t>
         </is>
       </c>
     </row>
@@ -39406,19 +39418,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="D87" s="30" t="inlineStr">
-        <is>
-          <t>(跨表)</t>
-        </is>
-      </c>
-      <c r="E87" s="30" t="inlineStr">
-        <is>
-          <t>无等价列</t>
+      <c r="D87" s="27" t="inlineStr">
+        <is>
+          <t>ACPLB.LB011</t>
+        </is>
+      </c>
+      <c r="E87" s="27" t="inlineStr">
+        <is>
+          <t>关联取得</t>
         </is>
       </c>
       <c r="F87" s="28" t="inlineStr">
         <is>
-          <t>⚠ ACPTK 单头无『增减别』列。易飞做法：异动台账查 ACPLB.LB011，单头查 ACPTK。需按模板口径二选一</t>
+          <t>★ 用户裁决：在 ACPLB.LB011（应付异动台账 方向 numeric ±1）取。与 YSFGQA.GQA020 同源同表。落地：payable_balance 的 WHERE 条件从 ACPTK 改为 ACPLB</t>
         </is>
       </c>
     </row>
@@ -39684,94 +39696,2274 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:D146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" style="3" min="1" max="1"/>
-    <col width="22" customWidth="1" style="3" min="2" max="2"/>
-    <col width="18" customWidth="1" style="3" min="3" max="3"/>
-    <col width="30" customWidth="1" style="3" min="4" max="4"/>
-    <col width="74" customWidth="1" style="3" min="5" max="5"/>
-    <col width="56" customWidth="1" style="3" min="6" max="6"/>
-    <col width="40" customWidth="1" style="3" min="7" max="7"/>
+    <col width="12" customWidth="1" style="3" min="1" max="1"/>
+    <col width="26" customWidth="1" style="3" min="2" max="2"/>
+    <col width="7" customWidth="1" style="3" min="3" max="3"/>
+    <col width="88" customWidth="1" style="3" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="31" t="inlineStr">
         <is>
-          <t>优先级</t>
+          <t>MQ003 码</t>
         </is>
       </c>
       <c r="B1" s="31" t="inlineStr">
         <is>
-          <t>易助字段</t>
+          <t>中文名（单据性质）</t>
         </is>
       </c>
       <c r="C1" s="31" t="inlineStr">
         <is>
-          <t>语义</t>
+          <t>关键</t>
         </is>
       </c>
       <c r="D1" s="31" t="inlineStr">
         <is>
-          <t>现状</t>
+          <t>说明 / 口径提示</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1" s="3">
+      <c r="A2" s="38" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B2" s="38" t="inlineStr">
+        <is>
+          <t>库存交易单</t>
+        </is>
+      </c>
+      <c r="C2" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D2" s="38" t="inlineStr">
+        <is>
+          <t>库存交易单（INVLA 最常见，18 个单别）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1" s="3">
+      <c r="A3" s="33" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B3" s="33" t="inlineStr">
+        <is>
+          <t>调拨单</t>
+        </is>
+      </c>
+      <c r="C3" s="33" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D3" s="33" t="inlineStr">
+        <is>
+          <t>调拨单</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1" s="3">
+      <c r="A4" s="33" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B4" s="33" t="inlineStr">
+        <is>
+          <t>借出单</t>
+        </is>
+      </c>
+      <c r="C4" s="33" t="inlineStr"/>
+      <c r="D4" s="33" t="inlineStr"/>
+    </row>
+    <row r="5" ht="28" customHeight="1" s="3">
+      <c r="A5" s="33" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B5" s="33" t="inlineStr">
+        <is>
+          <t>借入</t>
+        </is>
+      </c>
+      <c r="C5" s="33" t="inlineStr"/>
+      <c r="D5" s="33" t="inlineStr"/>
+    </row>
+    <row r="6" ht="28" customHeight="1" s="3">
+      <c r="A6" s="33" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B6" s="33" t="inlineStr">
+        <is>
+          <t>借出归还单</t>
+        </is>
+      </c>
+      <c r="C6" s="33" t="inlineStr"/>
+      <c r="D6" s="33" t="inlineStr"/>
+    </row>
+    <row r="7" ht="28" customHeight="1" s="3">
+      <c r="A7" s="33" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B7" s="33" t="inlineStr">
+        <is>
+          <t>借入归还单</t>
+        </is>
+      </c>
+      <c r="C7" s="33" t="inlineStr"/>
+      <c r="D7" s="33" t="inlineStr"/>
+    </row>
+    <row r="8" ht="28" customHeight="1" s="3">
+      <c r="A8" s="33" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B8" s="33" t="inlineStr">
+        <is>
+          <t>成本开账调整单</t>
+        </is>
+      </c>
+      <c r="C8" s="33" t="inlineStr"/>
+      <c r="D8" s="33" t="inlineStr"/>
+    </row>
+    <row r="9" ht="28" customHeight="1" s="3">
+      <c r="A9" s="33" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B9" s="33" t="inlineStr">
+        <is>
+          <t>报废单</t>
+        </is>
+      </c>
+      <c r="C9" s="33" t="inlineStr"/>
+      <c r="D9" s="33" t="inlineStr"/>
+    </row>
+    <row r="10" ht="28" customHeight="1" s="3">
+      <c r="A10" s="33" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B10" s="33" t="inlineStr">
+        <is>
+          <t>销毁单</t>
+        </is>
+      </c>
+      <c r="C10" s="33" t="inlineStr"/>
+      <c r="D10" s="33" t="inlineStr"/>
+    </row>
+    <row r="11" ht="28" customHeight="1" s="3">
+      <c r="A11" s="33" t="inlineStr">
+        <is>
+          <t>1A</t>
+        </is>
+      </c>
+      <c r="B11" s="33" t="inlineStr">
+        <is>
+          <t>装箱单</t>
+        </is>
+      </c>
+      <c r="C11" s="33" t="inlineStr"/>
+      <c r="D11" s="33" t="inlineStr"/>
+    </row>
+    <row r="12" ht="28" customHeight="1" s="3">
+      <c r="A12" s="33" t="inlineStr">
+        <is>
+          <t>1B</t>
+        </is>
+      </c>
+      <c r="B12" s="33" t="inlineStr">
+        <is>
+          <t>序号开账调整单</t>
+        </is>
+      </c>
+      <c r="C12" s="33" t="inlineStr"/>
+      <c r="D12" s="33" t="inlineStr"/>
+    </row>
+    <row r="13" ht="28" customHeight="1" s="3">
+      <c r="A13" s="33" t="inlineStr">
+        <is>
+          <t>1Z</t>
+        </is>
+      </c>
+      <c r="B13" s="33" t="inlineStr">
+        <is>
+          <t>在库料检验单</t>
+        </is>
+      </c>
+      <c r="C13" s="33" t="inlineStr"/>
+      <c r="D13" s="33" t="inlineStr"/>
+    </row>
+    <row r="14" ht="28" customHeight="1" s="3">
+      <c r="A14" s="33" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B14" s="33" t="inlineStr">
+        <is>
+          <t>报价单</t>
+        </is>
+      </c>
+      <c r="C14" s="33" t="inlineStr"/>
+      <c r="D14" s="33" t="inlineStr"/>
+    </row>
+    <row r="15" ht="28" customHeight="1" s="3">
+      <c r="A15" s="33" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B15" s="33" t="inlineStr">
+        <is>
+          <t>客户订单</t>
+        </is>
+      </c>
+      <c r="C15" s="33" t="inlineStr"/>
+      <c r="D15" s="33" t="inlineStr"/>
+    </row>
+    <row r="16" ht="28" customHeight="1" s="3">
+      <c r="A16" s="38" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B16" s="38" t="inlineStr">
+        <is>
+          <t>销货单</t>
+        </is>
+      </c>
+      <c r="C16" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D16" s="38" t="inlineStr">
+        <is>
+          <t>★★ 易助 LNA001='33'(销货) 的对应性质。INVLA 出库成本口径 = MQ003 IN ('23') + LA005=-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1" s="3">
+      <c r="A17" s="33" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B17" s="33" t="inlineStr">
+        <is>
+          <t>销退单</t>
+        </is>
+      </c>
+      <c r="C17" s="33" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D17" s="33" t="inlineStr">
+        <is>
+          <t>★ 销退单（易助销货退回）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1" s="3">
+      <c r="A18" s="33" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B18" s="33" t="inlineStr">
+        <is>
+          <t>出货通知单</t>
+        </is>
+      </c>
+      <c r="C18" s="33" t="inlineStr"/>
+      <c r="D18" s="33" t="inlineStr"/>
+    </row>
+    <row r="19" ht="28" customHeight="1" s="3">
+      <c r="A19" s="33" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B19" s="33" t="inlineStr">
+        <is>
+          <t>多角贸易订单</t>
+        </is>
+      </c>
+      <c r="C19" s="33" t="inlineStr"/>
+      <c r="D19" s="33" t="inlineStr"/>
+    </row>
+    <row r="20" ht="28" customHeight="1" s="3">
+      <c r="A20" s="33" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B20" s="33" t="inlineStr">
+        <is>
+          <t>多角贸易销货单</t>
+        </is>
+      </c>
+      <c r="C20" s="33" t="inlineStr"/>
+      <c r="D20" s="33" t="inlineStr"/>
+    </row>
+    <row r="21" ht="28" customHeight="1" s="3">
+      <c r="A21" s="33" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B21" s="33" t="inlineStr">
+        <is>
+          <t>多角贸易销退单</t>
+        </is>
+      </c>
+      <c r="C21" s="33" t="inlineStr"/>
+      <c r="D21" s="33" t="inlineStr"/>
+    </row>
+    <row r="22" ht="28" customHeight="1" s="3">
+      <c r="A22" s="33" t="inlineStr">
+        <is>
+          <t>2D</t>
+        </is>
+      </c>
+      <c r="B22" s="33" t="inlineStr">
+        <is>
+          <t>零组件发货单</t>
+        </is>
+      </c>
+      <c r="C22" s="33" t="inlineStr"/>
+      <c r="D22" s="33" t="inlineStr"/>
+    </row>
+    <row r="23" ht="28" customHeight="1" s="3">
+      <c r="A23" s="33" t="inlineStr">
+        <is>
+          <t>2E</t>
+        </is>
+      </c>
+      <c r="B23" s="33" t="inlineStr">
+        <is>
+          <t>安装调试通知单</t>
+        </is>
+      </c>
+      <c r="C23" s="33" t="inlineStr"/>
+      <c r="D23" s="33" t="inlineStr"/>
+    </row>
+    <row r="24" ht="28" customHeight="1" s="3">
+      <c r="A24" s="33" t="inlineStr">
+        <is>
+          <t>2F</t>
+        </is>
+      </c>
+      <c r="B24" s="33" t="inlineStr">
+        <is>
+          <t>安装调试单</t>
+        </is>
+      </c>
+      <c r="C24" s="33" t="inlineStr"/>
+      <c r="D24" s="33" t="inlineStr"/>
+    </row>
+    <row r="25" ht="28" customHeight="1" s="3">
+      <c r="A25" s="33" t="inlineStr">
+        <is>
+          <t>2S</t>
+        </is>
+      </c>
+      <c r="B25" s="33" t="inlineStr">
+        <is>
+          <t>合同</t>
+        </is>
+      </c>
+      <c r="C25" s="33" t="inlineStr"/>
+      <c r="D25" s="33" t="inlineStr"/>
+    </row>
+    <row r="26" ht="28" customHeight="1" s="3">
+      <c r="A26" s="33" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B26" s="33" t="inlineStr">
+        <is>
+          <t>请购单</t>
+        </is>
+      </c>
+      <c r="C26" s="33" t="inlineStr"/>
+      <c r="D26" s="33" t="inlineStr"/>
+    </row>
+    <row r="27" ht="28" customHeight="1" s="3">
+      <c r="A27" s="33" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B27" s="33" t="inlineStr">
+        <is>
+          <t>核价单</t>
+        </is>
+      </c>
+      <c r="C27" s="33" t="inlineStr"/>
+      <c r="D27" s="33" t="inlineStr"/>
+    </row>
+    <row r="28" ht="28" customHeight="1" s="3">
+      <c r="A28" s="39" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B28" s="39" t="inlineStr">
+        <is>
+          <t>采购单</t>
+        </is>
+      </c>
+      <c r="C28" s="39" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D28" s="39" t="inlineStr">
+        <is>
+          <t>⚠⚠ 陷阱：易飞 33=采购单，但易助 33=销货单。同码不同义，勿直接套用易助常量</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1" s="3">
+      <c r="A29" s="38" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B29" s="38" t="inlineStr">
+        <is>
+          <t>进货单</t>
+        </is>
+      </c>
+      <c r="C29" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D29" s="38" t="inlineStr">
+        <is>
+          <t>进货单（易助 JSKJDA/JDB 对应）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1" s="3">
+      <c r="A30" s="33" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B30" s="33" t="inlineStr">
+        <is>
+          <t>退货单</t>
+        </is>
+      </c>
+      <c r="C30" s="33" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D30" s="33" t="inlineStr">
+        <is>
+          <t>退货单</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1" s="3">
+      <c r="A31" s="33" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B31" s="33" t="inlineStr">
+        <is>
+          <t>询价单</t>
+        </is>
+      </c>
+      <c r="C31" s="33" t="inlineStr"/>
+      <c r="D31" s="33" t="inlineStr"/>
+    </row>
+    <row r="32" ht="28" customHeight="1" s="3">
+      <c r="A32" s="33" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B32" s="33" t="inlineStr">
+        <is>
+          <t>到货单</t>
+        </is>
+      </c>
+      <c r="C32" s="33" t="inlineStr"/>
+      <c r="D32" s="33" t="inlineStr"/>
+    </row>
+    <row r="33" ht="28" customHeight="1" s="3">
+      <c r="A33" s="33" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B33" s="33" t="inlineStr">
+        <is>
+          <t>BOM变更单</t>
+        </is>
+      </c>
+      <c r="C33" s="33" t="inlineStr"/>
+      <c r="D33" s="33" t="inlineStr"/>
+    </row>
+    <row r="34" ht="28" customHeight="1" s="3">
+      <c r="A34" s="33" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B34" s="33" t="inlineStr">
+        <is>
+          <t>组合单</t>
+        </is>
+      </c>
+      <c r="C34" s="33" t="inlineStr"/>
+      <c r="D34" s="33" t="inlineStr"/>
+    </row>
+    <row r="35" ht="28" customHeight="1" s="3">
+      <c r="A35" s="33" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B35" s="33" t="inlineStr">
+        <is>
+          <t>拆解单</t>
+        </is>
+      </c>
+      <c r="C35" s="33" t="inlineStr"/>
+      <c r="D35" s="33" t="inlineStr"/>
+    </row>
+    <row r="36" ht="28" customHeight="1" s="3">
+      <c r="A36" s="33" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B36" s="33" t="inlineStr">
+        <is>
+          <t>E-BOM变更单</t>
+        </is>
+      </c>
+      <c r="C36" s="33" t="inlineStr"/>
+      <c r="D36" s="33" t="inlineStr"/>
+    </row>
+    <row r="37" ht="28" customHeight="1" s="3">
+      <c r="A37" s="33" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B37" s="33" t="inlineStr">
+        <is>
+          <t>BOM单据</t>
+        </is>
+      </c>
+      <c r="C37" s="33" t="inlineStr"/>
+      <c r="D37" s="33" t="inlineStr"/>
+    </row>
+    <row r="38" ht="28" customHeight="1" s="3">
+      <c r="A38" s="33" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B38" s="33" t="inlineStr">
+        <is>
+          <t>一般工单</t>
+        </is>
+      </c>
+      <c r="C38" s="33" t="inlineStr"/>
+      <c r="D38" s="33" t="inlineStr"/>
+    </row>
+    <row r="39" ht="28" customHeight="1" s="3">
+      <c r="A39" s="33" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B39" s="33" t="inlineStr">
+        <is>
+          <t>返工工单</t>
+        </is>
+      </c>
+      <c r="C39" s="33" t="inlineStr"/>
+      <c r="D39" s="33" t="inlineStr"/>
+    </row>
+    <row r="40" ht="28" customHeight="1" s="3">
+      <c r="A40" s="33" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B40" s="33" t="inlineStr">
+        <is>
+          <t>拆件工单</t>
+        </is>
+      </c>
+      <c r="C40" s="33" t="inlineStr"/>
+      <c r="D40" s="33" t="inlineStr"/>
+    </row>
+    <row r="41" ht="28" customHeight="1" s="3">
+      <c r="A41" s="38" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="B41" s="38" t="inlineStr">
+        <is>
+          <t>厂内领料单</t>
+        </is>
+      </c>
+      <c r="C41" s="38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D41" s="38" t="inlineStr">
+        <is>
+          <t>★ 易助 LNA001='82'(领料) 的对应性质。厂内领料单</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1" s="3">
+      <c r="A42" s="33" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B42" s="33" t="inlineStr">
+        <is>
+          <t>委外领料单</t>
+        </is>
+      </c>
+      <c r="C42" s="33" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D42" s="33" t="inlineStr">
+        <is>
+          <t>委外领料单</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="28" customHeight="1" s="3">
+      <c r="A43" s="33" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B43" s="33" t="inlineStr">
+        <is>
+          <t>厂内退料单</t>
+        </is>
+      </c>
+      <c r="C43" s="33" t="inlineStr"/>
+      <c r="D43" s="33" t="inlineStr"/>
+    </row>
+    <row r="44" ht="28" customHeight="1" s="3">
+      <c r="A44" s="33" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B44" s="33" t="inlineStr">
+        <is>
+          <t>委外退料单</t>
+        </is>
+      </c>
+      <c r="C44" s="33" t="inlineStr"/>
+      <c r="D44" s="33" t="inlineStr"/>
+    </row>
+    <row r="45" ht="28" customHeight="1" s="3">
+      <c r="A45" s="33" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B45" s="33" t="inlineStr">
+        <is>
+          <t>生产入库单</t>
+        </is>
+      </c>
+      <c r="C45" s="33" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D45" s="33" t="inlineStr">
+        <is>
+          <t>生产入库单</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="28" customHeight="1" s="3">
+      <c r="A46" s="33" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B46" s="33" t="inlineStr">
+        <is>
+          <t>委外进货单</t>
+        </is>
+      </c>
+      <c r="C46" s="33" t="inlineStr"/>
+      <c r="D46" s="33" t="inlineStr"/>
+    </row>
+    <row r="47" ht="28" customHeight="1" s="3">
+      <c r="A47" s="33" t="inlineStr">
+        <is>
+          <t>5A</t>
+        </is>
+      </c>
+      <c r="B47" s="33" t="inlineStr">
+        <is>
+          <t>委外退货单</t>
+        </is>
+      </c>
+      <c r="C47" s="33" t="inlineStr"/>
+      <c r="D47" s="33" t="inlineStr"/>
+    </row>
+    <row r="48" ht="28" customHeight="1" s="3">
+      <c r="A48" s="33" t="inlineStr">
+        <is>
+          <t>5B</t>
+        </is>
+      </c>
+      <c r="B48" s="33" t="inlineStr">
+        <is>
+          <t>核价单</t>
+        </is>
+      </c>
+      <c r="C48" s="33" t="inlineStr"/>
+      <c r="D48" s="33" t="inlineStr"/>
+    </row>
+    <row r="49" ht="28" customHeight="1" s="3">
+      <c r="A49" s="33" t="inlineStr">
+        <is>
+          <t>5C</t>
+        </is>
+      </c>
+      <c r="B49" s="33" t="inlineStr">
+        <is>
+          <t>挪料单</t>
+        </is>
+      </c>
+      <c r="C49" s="33" t="inlineStr"/>
+      <c r="D49" s="33" t="inlineStr"/>
+    </row>
+    <row r="50" ht="28" customHeight="1" s="3">
+      <c r="A50" s="33" t="inlineStr">
+        <is>
+          <t>5D</t>
+        </is>
+      </c>
+      <c r="B50" s="33" t="inlineStr">
+        <is>
+          <t>委外到货单</t>
+        </is>
+      </c>
+      <c r="C50" s="33" t="inlineStr"/>
+      <c r="D50" s="33" t="inlineStr"/>
+    </row>
+    <row r="51" ht="28" customHeight="1" s="3">
+      <c r="A51" s="33" t="inlineStr">
+        <is>
+          <t>5E</t>
+        </is>
+      </c>
+      <c r="B51" s="33" t="inlineStr">
+        <is>
+          <t>入库转领料单</t>
+        </is>
+      </c>
+      <c r="C51" s="33" t="inlineStr"/>
+      <c r="D51" s="33" t="inlineStr"/>
+    </row>
+    <row r="52" ht="28" customHeight="1" s="3">
+      <c r="A52" s="33" t="inlineStr">
+        <is>
+          <t>5H</t>
+        </is>
+      </c>
+      <c r="B52" s="33" t="inlineStr">
+        <is>
+          <t>委外领料通知单</t>
+        </is>
+      </c>
+      <c r="C52" s="33" t="inlineStr"/>
+      <c r="D52" s="33" t="inlineStr"/>
+    </row>
+    <row r="53" ht="28" customHeight="1" s="3">
+      <c r="A53" s="33" t="inlineStr">
+        <is>
+          <t>5I</t>
+        </is>
+      </c>
+      <c r="B53" s="33" t="inlineStr">
+        <is>
+          <t>返工序号对应单</t>
+        </is>
+      </c>
+      <c r="C53" s="33" t="inlineStr"/>
+      <c r="D53" s="33" t="inlineStr"/>
+    </row>
+    <row r="54" ht="28" customHeight="1" s="3">
+      <c r="A54" s="33" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B54" s="33" t="inlineStr">
+        <is>
+          <t>销售发票</t>
+        </is>
+      </c>
+      <c r="C54" s="33" t="inlineStr"/>
+      <c r="D54" s="33" t="inlineStr"/>
+    </row>
+    <row r="55" ht="28" customHeight="1" s="3">
+      <c r="A55" s="33" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="B55" s="33" t="inlineStr">
+        <is>
+          <t>预收结账单</t>
+        </is>
+      </c>
+      <c r="C55" s="33" t="inlineStr"/>
+      <c r="D55" s="33" t="inlineStr"/>
+    </row>
+    <row r="56" ht="28" customHeight="1" s="3">
+      <c r="A56" s="33" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="B56" s="33" t="inlineStr">
+        <is>
+          <t>收款单</t>
+        </is>
+      </c>
+      <c r="C56" s="33" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D56" s="33" t="inlineStr">
+        <is>
+          <t>收款单（YSFGDA → ACRTK 对应）</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="28" customHeight="1" s="3">
+      <c r="A57" s="33" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="B57" s="33" t="inlineStr">
+        <is>
+          <t>预收结账单</t>
+        </is>
+      </c>
+      <c r="C57" s="33" t="inlineStr"/>
+      <c r="D57" s="33" t="inlineStr"/>
+    </row>
+    <row r="58" ht="28" customHeight="1" s="3">
+      <c r="A58" s="33" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="B58" s="33" t="inlineStr">
+        <is>
+          <t>预收待抵单</t>
+        </is>
+      </c>
+      <c r="C58" s="33" t="inlineStr"/>
+      <c r="D58" s="33" t="inlineStr"/>
+    </row>
+    <row r="59" ht="28" customHeight="1" s="3">
+      <c r="A59" s="33" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="B59" s="33" t="inlineStr">
+        <is>
+          <t>多角贸易结账单</t>
+        </is>
+      </c>
+      <c r="C59" s="33" t="inlineStr"/>
+      <c r="D59" s="33" t="inlineStr"/>
+    </row>
+    <row r="60" ht="28" customHeight="1" s="3">
+      <c r="A60" s="33" t="inlineStr">
+        <is>
+          <t>6A</t>
+        </is>
+      </c>
+      <c r="B60" s="33" t="inlineStr">
+        <is>
+          <t>预开发票</t>
+        </is>
+      </c>
+      <c r="C60" s="33" t="inlineStr"/>
+      <c r="D60" s="33" t="inlineStr"/>
+    </row>
+    <row r="61" ht="28" customHeight="1" s="3">
+      <c r="A61" s="33" t="inlineStr">
+        <is>
+          <t>6B</t>
+        </is>
+      </c>
+      <c r="B61" s="33" t="inlineStr">
+        <is>
+          <t>其他应收单</t>
+        </is>
+      </c>
+      <c r="C61" s="33" t="inlineStr"/>
+      <c r="D61" s="33" t="inlineStr"/>
+    </row>
+    <row r="62" ht="28" customHeight="1" s="3">
+      <c r="A62" s="33" t="inlineStr">
+        <is>
+          <t>6C</t>
+        </is>
+      </c>
+      <c r="B62" s="33" t="inlineStr">
+        <is>
+          <t>预收款单</t>
+        </is>
+      </c>
+      <c r="C62" s="33" t="inlineStr"/>
+      <c r="D62" s="33" t="inlineStr"/>
+    </row>
+    <row r="63" ht="28" customHeight="1" s="3">
+      <c r="A63" s="33" t="inlineStr">
+        <is>
+          <t>6D</t>
+        </is>
+      </c>
+      <c r="B63" s="33" t="inlineStr">
+        <is>
+          <t>退款单</t>
+        </is>
+      </c>
+      <c r="C63" s="33" t="inlineStr"/>
+      <c r="D63" s="33" t="inlineStr"/>
+    </row>
+    <row r="64" ht="28" customHeight="1" s="3">
+      <c r="A64" s="33" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="B64" s="33" t="inlineStr">
+        <is>
+          <t>坏账准备单</t>
+        </is>
+      </c>
+      <c r="C64" s="33" t="inlineStr"/>
+      <c r="D64" s="33" t="inlineStr"/>
+    </row>
+    <row r="65" ht="28" customHeight="1" s="3">
+      <c r="A65" s="33" t="inlineStr">
+        <is>
+          <t>6F</t>
+        </is>
+      </c>
+      <c r="B65" s="33" t="inlineStr">
+        <is>
+          <t>坏账损失处理单</t>
+        </is>
+      </c>
+      <c r="C65" s="33" t="inlineStr"/>
+      <c r="D65" s="33" t="inlineStr"/>
+    </row>
+    <row r="66" ht="28" customHeight="1" s="3">
+      <c r="A66" s="33" t="inlineStr">
+        <is>
+          <t>6G</t>
+        </is>
+      </c>
+      <c r="B66" s="33" t="inlineStr">
+        <is>
+          <t>汇差调整单</t>
+        </is>
+      </c>
+      <c r="C66" s="33" t="inlineStr"/>
+      <c r="D66" s="33" t="inlineStr"/>
+    </row>
+    <row r="67" ht="28" customHeight="1" s="3">
+      <c r="A67" s="33" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B67" s="33" t="inlineStr">
+        <is>
+          <t>采购发票</t>
+        </is>
+      </c>
+      <c r="C67" s="33" t="inlineStr"/>
+      <c r="D67" s="33" t="inlineStr"/>
+    </row>
+    <row r="68" ht="28" customHeight="1" s="3">
+      <c r="A68" s="33" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="B68" s="33" t="inlineStr">
+        <is>
+          <t>溢付待抵单</t>
+        </is>
+      </c>
+      <c r="C68" s="33" t="inlineStr"/>
+      <c r="D68" s="33" t="inlineStr"/>
+    </row>
+    <row r="69" ht="28" customHeight="1" s="3">
+      <c r="A69" s="33" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="B69" s="33" t="inlineStr">
+        <is>
+          <t>付款单</t>
+        </is>
+      </c>
+      <c r="C69" s="33" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D69" s="33" t="inlineStr">
+        <is>
+          <t>付款单（YSFGPA → ACPTK 对应）</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="28" customHeight="1" s="3">
+      <c r="A70" s="33" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="B70" s="33" t="inlineStr">
+        <is>
+          <t>预付结账单</t>
+        </is>
+      </c>
+      <c r="C70" s="33" t="inlineStr"/>
+      <c r="D70" s="33" t="inlineStr"/>
+    </row>
+    <row r="71" ht="28" customHeight="1" s="3">
+      <c r="A71" s="33" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="B71" s="33" t="inlineStr">
+        <is>
+          <t>预付待抵单</t>
+        </is>
+      </c>
+      <c r="C71" s="33" t="inlineStr"/>
+      <c r="D71" s="33" t="inlineStr"/>
+    </row>
+    <row r="72" ht="28" customHeight="1" s="3">
+      <c r="A72" s="33" t="inlineStr">
+        <is>
+          <t>7A</t>
+        </is>
+      </c>
+      <c r="B72" s="33" t="inlineStr">
+        <is>
+          <t>预开发票</t>
+        </is>
+      </c>
+      <c r="C72" s="33" t="inlineStr"/>
+      <c r="D72" s="33" t="inlineStr"/>
+    </row>
+    <row r="73" ht="28" customHeight="1" s="3">
+      <c r="A73" s="33" t="inlineStr">
+        <is>
+          <t>7B</t>
+        </is>
+      </c>
+      <c r="B73" s="33" t="inlineStr">
+        <is>
+          <t>其他应付</t>
+        </is>
+      </c>
+      <c r="C73" s="33" t="inlineStr"/>
+      <c r="D73" s="33" t="inlineStr"/>
+    </row>
+    <row r="74" ht="28" customHeight="1" s="3">
+      <c r="A74" s="33" t="inlineStr">
+        <is>
+          <t>7C</t>
+        </is>
+      </c>
+      <c r="B74" s="33" t="inlineStr">
+        <is>
+          <t>预付款单</t>
+        </is>
+      </c>
+      <c r="C74" s="33" t="inlineStr"/>
+      <c r="D74" s="33" t="inlineStr"/>
+    </row>
+    <row r="75" ht="28" customHeight="1" s="3">
+      <c r="A75" s="33" t="inlineStr">
+        <is>
+          <t>7D</t>
+        </is>
+      </c>
+      <c r="B75" s="33" t="inlineStr">
+        <is>
+          <t>应付退款单</t>
+        </is>
+      </c>
+      <c r="C75" s="33" t="inlineStr"/>
+      <c r="D75" s="33" t="inlineStr"/>
+    </row>
+    <row r="76" ht="28" customHeight="1" s="3">
+      <c r="A76" s="33" t="inlineStr">
+        <is>
+          <t>7E</t>
+        </is>
+      </c>
+      <c r="B76" s="33" t="inlineStr">
+        <is>
+          <t>汇差调整单</t>
+        </is>
+      </c>
+      <c r="C76" s="33" t="inlineStr"/>
+      <c r="D76" s="33" t="inlineStr"/>
+    </row>
+    <row r="77" ht="28" customHeight="1" s="3">
+      <c r="A77" s="33" t="inlineStr">
+        <is>
+          <t>7F</t>
+        </is>
+      </c>
+      <c r="B77" s="33" t="inlineStr">
+        <is>
+          <t>费用发票</t>
+        </is>
+      </c>
+      <c r="C77" s="33" t="inlineStr"/>
+      <c r="D77" s="33" t="inlineStr"/>
+    </row>
+    <row r="78" ht="28" customHeight="1" s="3">
+      <c r="A78" s="33" t="inlineStr">
+        <is>
+          <t>7G</t>
+        </is>
+      </c>
+      <c r="B78" s="33" t="inlineStr">
+        <is>
+          <t>暂估成本核算单</t>
+        </is>
+      </c>
+      <c r="C78" s="33" t="inlineStr"/>
+      <c r="D78" s="33" t="inlineStr"/>
+    </row>
+    <row r="79" ht="28" customHeight="1" s="3">
+      <c r="A79" s="33" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="B79" s="33" t="inlineStr">
+        <is>
+          <t>存款单据</t>
+        </is>
+      </c>
+      <c r="C79" s="33" t="inlineStr"/>
+      <c r="D79" s="33" t="inlineStr"/>
+    </row>
+    <row r="80" ht="28" customHeight="1" s="3">
+      <c r="A80" s="39" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="B80" s="39" t="inlineStr">
+        <is>
+          <t>提款单据</t>
+        </is>
+      </c>
+      <c r="C80" s="39" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D80" s="39" t="inlineStr">
+        <is>
+          <t>⚠⚠ 陷阱：易飞 82=提款单据（财务），易助 82=领料单。同码不同义</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="28" customHeight="1" s="3">
+      <c r="A81" s="33" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="B81" s="33" t="inlineStr">
+        <is>
+          <t>融资托票</t>
+        </is>
+      </c>
+      <c r="C81" s="33" t="inlineStr"/>
+      <c r="D81" s="33" t="inlineStr"/>
+    </row>
+    <row r="82" ht="28" customHeight="1" s="3">
+      <c r="A82" s="39" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="B82" s="39" t="inlineStr">
+        <is>
+          <t>融资借款</t>
+        </is>
+      </c>
+      <c r="C82" s="39" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D82" s="39" t="inlineStr">
+        <is>
+          <t>⚠⚠ 陷阱：易飞 84=融资借款（财务），易助 84=生产耗用。同码不同义</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="28" customHeight="1" s="3">
+      <c r="A83" s="39" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="B83" s="39" t="inlineStr">
+        <is>
+          <t>融资还款</t>
+        </is>
+      </c>
+      <c r="C83" s="39" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D83" s="39" t="inlineStr">
+        <is>
+          <t>⚠⚠ 陷阱：易飞 85=融资还款（财务），易助 85=生产耗用。同码不同义</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="28" customHeight="1" s="3">
+      <c r="A84" s="33" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="B84" s="33" t="inlineStr">
+        <is>
+          <t>抵押借款</t>
+        </is>
+      </c>
+      <c r="C84" s="33" t="inlineStr"/>
+      <c r="D84" s="33" t="inlineStr"/>
+    </row>
+    <row r="85" ht="28" customHeight="1" s="3">
+      <c r="A85" s="33" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="B85" s="33" t="inlineStr">
+        <is>
+          <t>抵押还款</t>
+        </is>
+      </c>
+      <c r="C85" s="33" t="inlineStr"/>
+      <c r="D85" s="33" t="inlineStr"/>
+    </row>
+    <row r="86" ht="28" customHeight="1" s="3">
+      <c r="A86" s="33" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="B86" s="33" t="inlineStr">
+        <is>
+          <t>调整汇率单</t>
+        </is>
+      </c>
+      <c r="C86" s="33" t="inlineStr"/>
+      <c r="D86" s="33" t="inlineStr"/>
+    </row>
+    <row r="87" ht="28" customHeight="1" s="3">
+      <c r="A87" s="33" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="B87" s="33" t="inlineStr">
+        <is>
+          <t>转账凭证</t>
+        </is>
+      </c>
+      <c r="C87" s="33" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D87" s="33" t="inlineStr">
+        <is>
+          <t>转账凭证（KJSNFA → ACTLE 相关，单别最多 27 个）</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="28" customHeight="1" s="3">
+      <c r="A88" s="33" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="B88" s="33" t="inlineStr">
+        <is>
+          <t>现收凭证</t>
+        </is>
+      </c>
+      <c r="C88" s="33" t="inlineStr"/>
+      <c r="D88" s="33" t="inlineStr"/>
+    </row>
+    <row r="89" ht="28" customHeight="1" s="3">
+      <c r="A89" s="33" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="B89" s="33" t="inlineStr">
+        <is>
+          <t>现支凭证</t>
+        </is>
+      </c>
+      <c r="C89" s="33" t="inlineStr"/>
+      <c r="D89" s="33" t="inlineStr"/>
+    </row>
+    <row r="90" ht="28" customHeight="1" s="3">
+      <c r="A90" s="33" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B90" s="33" t="inlineStr">
+        <is>
+          <t>预付购料单据</t>
+        </is>
+      </c>
+      <c r="C90" s="33" t="inlineStr"/>
+      <c r="D90" s="33" t="inlineStr"/>
+    </row>
+    <row r="91" ht="28" customHeight="1" s="3">
+      <c r="A91" s="33" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B91" s="33" t="inlineStr">
+        <is>
+          <t>报关单据</t>
+        </is>
+      </c>
+      <c r="C91" s="33" t="inlineStr"/>
+      <c r="D91" s="33" t="inlineStr"/>
+    </row>
+    <row r="92" ht="28" customHeight="1" s="3">
+      <c r="A92" s="33" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B92" s="33" t="inlineStr">
+        <is>
+          <t>出货通知单</t>
+        </is>
+      </c>
+      <c r="C92" s="33" t="inlineStr"/>
+      <c r="D92" s="33" t="inlineStr"/>
+    </row>
+    <row r="93" ht="28" customHeight="1" s="3">
+      <c r="A93" s="33" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B93" s="33" t="inlineStr">
+        <is>
+          <t>货运通知单</t>
+        </is>
+      </c>
+      <c r="C93" s="33" t="inlineStr"/>
+      <c r="D93" s="33" t="inlineStr"/>
+    </row>
+    <row r="94" ht="28" customHeight="1" s="3">
+      <c r="A94" s="33" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B94" s="33" t="inlineStr">
+        <is>
+          <t>出口费用单</t>
+        </is>
+      </c>
+      <c r="C94" s="33" t="inlineStr"/>
+      <c r="D94" s="33" t="inlineStr"/>
+    </row>
+    <row r="95" ht="28" customHeight="1" s="3">
+      <c r="A95" s="33" t="inlineStr">
+        <is>
+          <t>C0</t>
+        </is>
+      </c>
+      <c r="B95" s="33" t="inlineStr">
+        <is>
+          <t>取得</t>
+        </is>
+      </c>
+      <c r="C95" s="33" t="inlineStr"/>
+      <c r="D95" s="33" t="inlineStr"/>
+    </row>
+    <row r="96" ht="28" customHeight="1" s="3">
+      <c r="A96" s="33" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B96" s="33" t="inlineStr">
+        <is>
+          <t>改良</t>
+        </is>
+      </c>
+      <c r="C96" s="33" t="inlineStr"/>
+      <c r="D96" s="33" t="inlineStr"/>
+    </row>
+    <row r="97" ht="28" customHeight="1" s="3">
+      <c r="A97" s="33" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B97" s="33" t="inlineStr">
+        <is>
+          <t>重估</t>
+        </is>
+      </c>
+      <c r="C97" s="33" t="inlineStr"/>
+      <c r="D97" s="33" t="inlineStr"/>
+    </row>
+    <row r="98" ht="28" customHeight="1" s="3">
+      <c r="A98" s="33" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B98" s="33" t="inlineStr">
+        <is>
+          <t>报废</t>
+        </is>
+      </c>
+      <c r="C98" s="33" t="inlineStr"/>
+      <c r="D98" s="33" t="inlineStr"/>
+    </row>
+    <row r="99" ht="28" customHeight="1" s="3">
+      <c r="A99" s="33" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B99" s="33" t="inlineStr">
+        <is>
+          <t>出售</t>
+        </is>
+      </c>
+      <c r="C99" s="33" t="inlineStr"/>
+      <c r="D99" s="33" t="inlineStr"/>
+    </row>
+    <row r="100" ht="28" customHeight="1" s="3">
+      <c r="A100" s="33" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="B100" s="33" t="inlineStr">
+        <is>
+          <t>调整</t>
+        </is>
+      </c>
+      <c r="C100" s="33" t="inlineStr"/>
+      <c r="D100" s="33" t="inlineStr"/>
+    </row>
+    <row r="101" ht="28" customHeight="1" s="3">
+      <c r="A101" s="33" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="B101" s="33" t="inlineStr">
+        <is>
+          <t>折旧</t>
+        </is>
+      </c>
+      <c r="C101" s="33" t="inlineStr"/>
+      <c r="D101" s="33" t="inlineStr"/>
+    </row>
+    <row r="102" ht="28" customHeight="1" s="3">
+      <c r="A102" s="33" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="B102" s="33" t="inlineStr">
+        <is>
+          <t>转移</t>
+        </is>
+      </c>
+      <c r="C102" s="33" t="inlineStr"/>
+      <c r="D102" s="33" t="inlineStr"/>
+    </row>
+    <row r="103" ht="28" customHeight="1" s="3">
+      <c r="A103" s="33" t="inlineStr">
+        <is>
+          <t>C8</t>
+        </is>
+      </c>
+      <c r="B103" s="33" t="inlineStr">
+        <is>
+          <t>外送</t>
+        </is>
+      </c>
+      <c r="C103" s="33" t="inlineStr"/>
+      <c r="D103" s="33" t="inlineStr"/>
+    </row>
+    <row r="104" ht="28" customHeight="1" s="3">
+      <c r="A104" s="33" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="B104" s="33" t="inlineStr">
+        <is>
+          <t>收回</t>
+        </is>
+      </c>
+      <c r="C104" s="33" t="inlineStr"/>
+      <c r="D104" s="33" t="inlineStr"/>
+    </row>
+    <row r="105" ht="28" customHeight="1" s="3">
+      <c r="A105" s="33" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B105" s="33" t="inlineStr">
+        <is>
+          <t>资产请购</t>
+        </is>
+      </c>
+      <c r="C105" s="33" t="inlineStr"/>
+      <c r="D105" s="33" t="inlineStr"/>
+    </row>
+    <row r="106" ht="28" customHeight="1" s="3">
+      <c r="A106" s="33" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="B106" s="33" t="inlineStr">
+        <is>
+          <t>资产采购</t>
+        </is>
+      </c>
+      <c r="C106" s="33" t="inlineStr"/>
+      <c r="D106" s="33" t="inlineStr"/>
+    </row>
+    <row r="107" ht="28" customHeight="1" s="3">
+      <c r="A107" s="33" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="B107" s="33" t="inlineStr">
+        <is>
+          <t>资产进货</t>
+        </is>
+      </c>
+      <c r="C107" s="33" t="inlineStr"/>
+      <c r="D107" s="33" t="inlineStr"/>
+    </row>
+    <row r="108" ht="28" customHeight="1" s="3">
+      <c r="A108" s="33" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
+      <c r="B108" s="33" t="inlineStr">
+        <is>
+          <t>减值准备</t>
+        </is>
+      </c>
+      <c r="C108" s="33" t="inlineStr"/>
+      <c r="D108" s="33" t="inlineStr"/>
+    </row>
+    <row r="109" ht="28" customHeight="1" s="3">
+      <c r="A109" s="33" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="B109" s="33" t="inlineStr">
+        <is>
+          <t>在建工程</t>
+        </is>
+      </c>
+      <c r="C109" s="33" t="inlineStr"/>
+      <c r="D109" s="33" t="inlineStr"/>
+    </row>
+    <row r="110" ht="28" customHeight="1" s="3">
+      <c r="A110" s="33" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B110" s="33" t="inlineStr">
+        <is>
+          <t>投产单</t>
+        </is>
+      </c>
+      <c r="C110" s="33" t="inlineStr"/>
+      <c r="D110" s="33" t="inlineStr"/>
+    </row>
+    <row r="111" ht="28" customHeight="1" s="3">
+      <c r="A111" s="33" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B111" s="33" t="inlineStr">
+        <is>
+          <t>转移单</t>
+        </is>
+      </c>
+      <c r="C111" s="33" t="inlineStr"/>
+      <c r="D111" s="33" t="inlineStr"/>
+    </row>
+    <row r="112" ht="28" customHeight="1" s="3">
+      <c r="A112" s="33" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="B112" s="33" t="inlineStr">
+        <is>
+          <t>入库单</t>
+        </is>
+      </c>
+      <c r="C112" s="33" t="inlineStr"/>
+      <c r="D112" s="33" t="inlineStr"/>
+    </row>
+    <row r="113" ht="28" customHeight="1" s="3">
+      <c r="A113" s="33" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="B113" s="33" t="inlineStr">
+        <is>
+          <t>报工单</t>
+        </is>
+      </c>
+      <c r="C113" s="33" t="inlineStr"/>
+      <c r="D113" s="33" t="inlineStr"/>
+    </row>
+    <row r="114" ht="28" customHeight="1" s="3">
+      <c r="A114" s="33" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B114" s="33" t="inlineStr">
+        <is>
+          <t>叫修单</t>
+        </is>
+      </c>
+      <c r="C114" s="33" t="inlineStr"/>
+      <c r="D114" s="33" t="inlineStr"/>
+    </row>
+    <row r="115" ht="28" customHeight="1" s="3">
+      <c r="A115" s="33" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B115" s="33" t="inlineStr">
+        <is>
+          <t>维修单</t>
+        </is>
+      </c>
+      <c r="C115" s="33" t="inlineStr"/>
+      <c r="D115" s="33" t="inlineStr"/>
+    </row>
+    <row r="116" ht="28" customHeight="1" s="3">
+      <c r="A116" s="33" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="B116" s="33" t="inlineStr">
+        <is>
+          <t>送原厂维修单</t>
+        </is>
+      </c>
+      <c r="C116" s="33" t="inlineStr"/>
+      <c r="D116" s="33" t="inlineStr"/>
+    </row>
+    <row r="117" ht="28" customHeight="1" s="3">
+      <c r="A117" s="33" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="B117" s="33" t="inlineStr">
+        <is>
+          <t>原厂修毕送回单</t>
+        </is>
+      </c>
+      <c r="C117" s="33" t="inlineStr"/>
+      <c r="D117" s="33" t="inlineStr"/>
+    </row>
+    <row r="118" ht="28" customHeight="1" s="3">
+      <c r="A118" s="33" t="inlineStr">
+        <is>
+          <t>I1</t>
+        </is>
+      </c>
+      <c r="B118" s="33" t="inlineStr">
+        <is>
+          <t>合同变更单据</t>
+        </is>
+      </c>
+      <c r="C118" s="33" t="inlineStr"/>
+      <c r="D118" s="33" t="inlineStr"/>
+    </row>
+    <row r="119" ht="28" customHeight="1" s="3">
+      <c r="A119" s="33" t="inlineStr">
+        <is>
+          <t>I2</t>
+        </is>
+      </c>
+      <c r="B119" s="33" t="inlineStr">
+        <is>
+          <t>结转单据</t>
+        </is>
+      </c>
+      <c r="C119" s="33" t="inlineStr"/>
+      <c r="D119" s="33" t="inlineStr"/>
+    </row>
+    <row r="120" ht="28" customHeight="1" s="3">
+      <c r="A120" s="33" t="inlineStr">
+        <is>
+          <t>I3</t>
+        </is>
+      </c>
+      <c r="B120" s="33" t="inlineStr">
+        <is>
+          <t>交易单据</t>
+        </is>
+      </c>
+      <c r="C120" s="33" t="inlineStr"/>
+      <c r="D120" s="33" t="inlineStr"/>
+    </row>
+    <row r="121" ht="28" customHeight="1" s="3">
+      <c r="A121" s="33" t="inlineStr">
+        <is>
+          <t>I4</t>
+        </is>
+      </c>
+      <c r="B121" s="33" t="inlineStr">
+        <is>
+          <t>转厂申请单据</t>
+        </is>
+      </c>
+      <c r="C121" s="33" t="inlineStr"/>
+      <c r="D121" s="33" t="inlineStr"/>
+    </row>
+    <row r="122" ht="28" customHeight="1" s="3">
+      <c r="A122" s="33" t="inlineStr">
+        <is>
+          <t>I5</t>
+        </is>
+      </c>
+      <c r="B122" s="33" t="inlineStr">
+        <is>
+          <t>退转厂维护单据</t>
+        </is>
+      </c>
+      <c r="C122" s="33" t="inlineStr"/>
+      <c r="D122" s="33" t="inlineStr"/>
+    </row>
+    <row r="123" ht="28" customHeight="1" s="3">
+      <c r="A123" s="33" t="inlineStr">
+        <is>
+          <t>I6</t>
+        </is>
+      </c>
+      <c r="B123" s="33" t="inlineStr">
+        <is>
+          <t>设备申请单据</t>
+        </is>
+      </c>
+      <c r="C123" s="33" t="inlineStr"/>
+      <c r="D123" s="33" t="inlineStr"/>
+    </row>
+    <row r="124" ht="28" customHeight="1" s="3">
+      <c r="A124" s="33" t="inlineStr">
+        <is>
+          <t>I7</t>
+        </is>
+      </c>
+      <c r="B124" s="33" t="inlineStr">
+        <is>
+          <t>设备维护单据</t>
+        </is>
+      </c>
+      <c r="C124" s="33" t="inlineStr"/>
+      <c r="D124" s="33" t="inlineStr"/>
+    </row>
+    <row r="125" ht="28" customHeight="1" s="3">
+      <c r="A125" s="33" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="B125" s="33" t="inlineStr">
+        <is>
+          <t>费用申请单</t>
+        </is>
+      </c>
+      <c r="C125" s="33" t="inlineStr"/>
+      <c r="D125" s="33" t="inlineStr"/>
+    </row>
+    <row r="126" ht="28" customHeight="1" s="3">
+      <c r="A126" s="33" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+      <c r="B126" s="33" t="inlineStr">
+        <is>
+          <t>费用借款单</t>
+        </is>
+      </c>
+      <c r="C126" s="33" t="inlineStr"/>
+      <c r="D126" s="33" t="inlineStr"/>
+    </row>
+    <row r="127" ht="28" customHeight="1" s="3">
+      <c r="A127" s="33" t="inlineStr">
+        <is>
+          <t>K3</t>
+        </is>
+      </c>
+      <c r="B127" s="33" t="inlineStr">
+        <is>
+          <t>费用还款单</t>
+        </is>
+      </c>
+      <c r="C127" s="33" t="inlineStr"/>
+      <c r="D127" s="33" t="inlineStr"/>
+    </row>
+    <row r="128" ht="28" customHeight="1" s="3">
+      <c r="A128" s="33" t="inlineStr">
+        <is>
+          <t>K4</t>
+        </is>
+      </c>
+      <c r="B128" s="33" t="inlineStr">
+        <is>
+          <t>费用报销单</t>
+        </is>
+      </c>
+      <c r="C128" s="33" t="inlineStr"/>
+      <c r="D128" s="33" t="inlineStr"/>
+    </row>
+    <row r="129" ht="28" customHeight="1" s="3">
+      <c r="A129" s="33" t="inlineStr">
+        <is>
+          <t>K5</t>
+        </is>
+      </c>
+      <c r="B129" s="33" t="inlineStr">
+        <is>
+          <t>费用调整单</t>
+        </is>
+      </c>
+      <c r="C129" s="33" t="inlineStr"/>
+      <c r="D129" s="33" t="inlineStr"/>
+    </row>
+    <row r="130" ht="28" customHeight="1" s="3">
+      <c r="A130" s="33" t="inlineStr">
+        <is>
+          <t>K6</t>
+        </is>
+      </c>
+      <c r="B130" s="33" t="inlineStr">
+        <is>
+          <t>费用预算单</t>
+        </is>
+      </c>
+      <c r="C130" s="33" t="inlineStr"/>
+      <c r="D130" s="33" t="inlineStr"/>
+    </row>
+    <row r="131" ht="28" customHeight="1" s="3">
+      <c r="A131" s="33" t="inlineStr">
+        <is>
+          <t>K7</t>
+        </is>
+      </c>
+      <c r="B131" s="33" t="inlineStr">
+        <is>
+          <t>费用预算调整单</t>
+        </is>
+      </c>
+      <c r="C131" s="33" t="inlineStr"/>
+      <c r="D131" s="33" t="inlineStr"/>
+    </row>
+    <row r="132" ht="28" customHeight="1" s="3">
+      <c r="A132" s="33" t="inlineStr">
+        <is>
+          <t>K8</t>
+        </is>
+      </c>
+      <c r="B132" s="33" t="inlineStr">
+        <is>
+          <t>其他费用申请单</t>
+        </is>
+      </c>
+      <c r="C132" s="33" t="inlineStr"/>
+      <c r="D132" s="33" t="inlineStr"/>
+    </row>
+    <row r="133" ht="28" customHeight="1" s="3">
+      <c r="A133" s="33" t="inlineStr">
+        <is>
+          <t>K9</t>
+        </is>
+      </c>
+      <c r="B133" s="33" t="inlineStr">
+        <is>
+          <t>其他费用单</t>
+        </is>
+      </c>
+      <c r="C133" s="33" t="inlineStr"/>
+      <c r="D133" s="33" t="inlineStr"/>
+    </row>
+    <row r="134" ht="28" customHeight="1" s="3">
+      <c r="A134" s="33" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="B134" s="33" t="inlineStr">
+        <is>
+          <t>内部订单</t>
+        </is>
+      </c>
+      <c r="C134" s="33" t="inlineStr"/>
+      <c r="D134" s="33" t="inlineStr"/>
+    </row>
+    <row r="135" ht="28" customHeight="1" s="3">
+      <c r="A135" s="33" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="B135" s="33" t="inlineStr">
+        <is>
+          <t>调拨出库单</t>
+        </is>
+      </c>
+      <c r="C135" s="33" t="inlineStr"/>
+      <c r="D135" s="33" t="inlineStr"/>
+    </row>
+    <row r="136" ht="28" customHeight="1" s="3">
+      <c r="A136" s="33" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="B136" s="33" t="inlineStr">
+        <is>
+          <t>调拨出库到达单</t>
+        </is>
+      </c>
+      <c r="C136" s="33" t="inlineStr"/>
+      <c r="D136" s="33" t="inlineStr"/>
+    </row>
+    <row r="137" ht="28" customHeight="1" s="3">
+      <c r="A137" s="33" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="B137" s="33" t="inlineStr">
+        <is>
+          <t>退货申请单</t>
+        </is>
+      </c>
+      <c r="C137" s="33" t="inlineStr"/>
+      <c r="D137" s="33" t="inlineStr"/>
+    </row>
+    <row r="138" ht="28" customHeight="1" s="3">
+      <c r="A138" s="33" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="B138" s="33" t="inlineStr">
+        <is>
+          <t>调拨退库单</t>
+        </is>
+      </c>
+      <c r="C138" s="33" t="inlineStr"/>
+      <c r="D138" s="33" t="inlineStr"/>
+    </row>
+    <row r="139" ht="28" customHeight="1" s="3">
+      <c r="A139" s="33" t="inlineStr">
+        <is>
+          <t>S6</t>
+        </is>
+      </c>
+      <c r="B139" s="33" t="inlineStr">
+        <is>
+          <t>调拨退库到达单</t>
+        </is>
+      </c>
+      <c r="C139" s="33" t="inlineStr"/>
+      <c r="D139" s="33" t="inlineStr"/>
+    </row>
+    <row r="140" ht="28" customHeight="1" s="3">
+      <c r="A140" s="33" t="inlineStr">
+        <is>
+          <t>S7</t>
+        </is>
+      </c>
+      <c r="B140" s="33" t="inlineStr">
+        <is>
+          <t>营业日报</t>
+        </is>
+      </c>
+      <c r="C140" s="33" t="inlineStr"/>
+      <c r="D140" s="33" t="inlineStr"/>
+    </row>
+    <row r="141" ht="28" customHeight="1" s="3">
+      <c r="A141" s="33" t="inlineStr">
+        <is>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="B141" s="33" t="inlineStr">
+        <is>
+          <t>调价单</t>
+        </is>
+      </c>
+      <c r="C141" s="33" t="inlineStr"/>
+      <c r="D141" s="33" t="inlineStr"/>
+    </row>
+    <row r="142" ht="28" customHeight="1" s="3">
+      <c r="A142" s="33" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="B142" s="33" t="inlineStr">
+        <is>
+          <t>人力需求单</t>
+        </is>
+      </c>
+      <c r="C142" s="33" t="inlineStr"/>
+      <c r="D142" s="33" t="inlineStr"/>
+    </row>
+    <row r="143" ht="28" customHeight="1" s="3">
+      <c r="A143" s="33" t="inlineStr">
+        <is>
+          <t>X2</t>
+        </is>
+      </c>
+      <c r="B143" s="33" t="inlineStr">
+        <is>
+          <t>培训申请单</t>
+        </is>
+      </c>
+      <c r="C143" s="33" t="inlineStr"/>
+      <c r="D143" s="33" t="inlineStr"/>
+    </row>
+    <row r="144" ht="28" customHeight="1" s="3">
+      <c r="A144" s="33" t="inlineStr">
+        <is>
+          <t>X3</t>
+        </is>
+      </c>
+      <c r="B144" s="33" t="inlineStr">
+        <is>
+          <t>培训结案单</t>
+        </is>
+      </c>
+      <c r="C144" s="33" t="inlineStr"/>
+      <c r="D144" s="33" t="inlineStr"/>
+    </row>
+    <row r="145" ht="28" customHeight="1" s="3">
+      <c r="A145" s="33" t="inlineStr">
+        <is>
+          <t>Y1</t>
+        </is>
+      </c>
+      <c r="B145" s="33" t="inlineStr">
+        <is>
+          <t>留样单</t>
+        </is>
+      </c>
+      <c r="C145" s="33" t="inlineStr"/>
+      <c r="D145" s="33" t="inlineStr"/>
+    </row>
+    <row r="146" ht="28" customHeight="1" s="3">
+      <c r="A146" s="33" t="inlineStr">
+        <is>
+          <t>Y4</t>
+        </is>
+      </c>
+      <c r="B146" s="33" t="inlineStr">
+        <is>
+          <t>检验单</t>
+        </is>
+      </c>
+      <c r="C146" s="33" t="inlineStr"/>
+      <c r="D146" s="33" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" style="3" min="1" max="1"/>
+    <col width="22" customWidth="1" style="3" min="2" max="2"/>
+    <col width="14" customWidth="1" style="3" min="3" max="3"/>
+    <col width="30" customWidth="1" style="3" min="4" max="4"/>
+    <col width="96" customWidth="1" style="3" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>原优先级</t>
+        </is>
+      </c>
+      <c r="B1" s="31" t="inlineStr">
+        <is>
+          <t>字段</t>
+        </is>
+      </c>
+      <c r="C1" s="31" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="D1" s="31" t="inlineStr">
+        <is>
+          <t>用户裁决（2026-10-09）</t>
         </is>
       </c>
       <c r="E1" s="31" t="inlineStr">
         <is>
-          <t>实测证据 / 裁决依据</t>
-        </is>
-      </c>
-      <c r="F1" s="31" t="inlineStr">
-        <is>
-          <t>建议方案</t>
-        </is>
-      </c>
-      <c r="G1" s="31" t="inlineStr">
-        <is>
-          <t>影响面</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="96" customHeight="1" s="3">
-      <c r="A2" s="32" t="inlineStr">
+          <t>落地方式 / 依据</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="88" customHeight="1" s="3">
+      <c r="A2" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
       <c r="B2" s="33" t="inlineStr">
         <is>
-          <t>JSKLPB.LPB005</t>
+          <t>JSKLPB.LPB005
+（仓库级期末成本）</t>
         </is>
       </c>
       <c r="C2" s="33" t="inlineStr">
         <is>
-          <t>仓库级期末成本</t>
+          <t>已裁决 · 降级</t>
         </is>
       </c>
       <c r="D2" s="33" t="inlineStr">
         <is>
-          <t>用户已确认 INVML / INVLE『只有数量没有成本』</t>
+          <t>inventory_by_batch 模板降级为仅数量</t>
         </is>
       </c>
       <c r="E2" s="33" t="inlineStr">
         <is>
-          <t>实测 INVLE 48 个业务列中，成本列 LE007/LE009/LE011/LE013/LE015/LE017/LE019/LE021/LE023/LE025/LE027 及四要素 LE028~LE031 全部恒为 0；INVML.MC008 不存在，ML012 是 0/1 标志位（0:649行/1:346行）不是成本。INV2-003.SDD 官方定义确认这些列名虽为『预留字段』但备注写的是『月初成本/本月入库金额』—— 即设计上未启用</t>
-        </is>
-      </c>
-      <c r="F2" s="33" t="inlineStr">
-        <is>
-          <t>① 仓库级期末成本改由 INVLC 按品号+仓库汇总（INVLC 有完整成本列 LC005~LC025）—— 可行② 批号级成本无法还原，inventory_by_batch 模板需降级为仅数量或明确标注成本缺失</t>
-        </is>
-      </c>
-      <c r="G2" s="33" t="inlineStr">
-        <is>
-          <t>inventory_asof / inventory_asof_by_warehouse / inventory_by_batch 三个模板</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="96" customHeight="1" s="3">
-      <c r="A3" s="34" t="inlineStr">
+          <t>① INVLE 无成本列（实测 LE007~LE027 成本位及四要素 371 行全零），批号级成本不可还原→ inventory_by_batch 视图仅输出数量，明确标注成本缺失
+② 仓库级期末成本仍可由 INVLC 的 4.2 公式按品号+仓库汇总得到（141/141 实测吻合）→ inventory_asof / inventory_asof_by_warehouse 不受影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="88" customHeight="1" s="3">
+      <c r="A3" s="33" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -39783,32 +41975,22 @@
       </c>
       <c r="C3" s="33" t="inlineStr">
         <is>
-          <t>过滤字段（&gt;0）</t>
+          <t>已裁决 · 换列</t>
         </is>
       </c>
       <c r="D3" s="33" t="inlineStr">
         <is>
-          <t>仍待确认过滤意图</t>
+          <t>过滤意图是「实际已交量」</t>
         </is>
       </c>
       <c r="E3" s="33" t="inlineStr">
         <is>
-          <t>templates.ts:281 `WHERE KEB021 = :approve_status AND KEB011 &gt; 0`（与审核码并列使用）。易飞 COPTH 无『已交量/已出货量』列；最接近 TH008 数量、TH042 已开票数量</t>
-        </is>
-      </c>
-      <c r="F3" s="33" t="inlineStr">
-        <is>
-          <t>① 若原意仅是排除赠品/零行 → 改用 TH008 &gt; 0② 若原意是『实际已交量』→ 易飞无等价列，需改用 TH008 或去掉该过滤</t>
-        </is>
-      </c>
-      <c r="G3" s="33" t="inlineStr">
-        <is>
-          <t>revenue_by_product 收入聚合</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="96" customHeight="1" s="3">
-      <c r="A4" s="34" t="inlineStr">
+          <t>易助 KEB011 = 实际已交量，用作 &gt;0 过滤。易飞 COPTH 无同名列，最接近的替代列是 TH008（数量，实测有值）。落地：SQL 条件改为 TH008 &gt; 0，并在视图列注释标注『易助 KEB011=实际已交量 → 易飞以 TH008 数量近似』。⚠ 若 TH008 非已交量口径，需在真实数据环境复核（测试库 COPTH 缺『已交量』列，无法验证）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="88" customHeight="1" s="3">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -39820,27 +42002,17 @@
       </c>
       <c r="C4" s="33" t="inlineStr">
         <is>
-          <t>应付增减别</t>
+          <t>已裁决 · 换表</t>
         </is>
       </c>
       <c r="D4" s="33" t="inlineStr">
         <is>
-          <t>ACPTK 单头无对应列</t>
+          <t>在 ACPLB.LB011（异动台账）</t>
         </is>
       </c>
       <c r="E4" s="33" t="inlineStr">
         <is>
-          <t>实测 ACPTK（付款单主档）无『方向/增减别』列；而 ACPLB（应付异动档）LB011 才是 numeric ±1。两张表语义分工：ACPTK=单据、ACPLB=异动台账</t>
-        </is>
-      </c>
-      <c r="F4" s="33" t="inlineStr">
-        <is>
-          <t>① 若模板口径是『应付异动余额』→ 应改查 ACPLB（与 YSFGQA.GQA020 同源）② 若口径是『付款单头』→ 去掉该过滤条件</t>
-        </is>
-      </c>
-      <c r="G4" s="33" t="inlineStr">
-        <is>
-          <t>应付余额类模板（payable_balance）</t>
+          <t>应付增减别改查 ACPLB.LB011（方向 numeric ±1，实测 1/-1 两值）。→ 与 YSFGQA.GQA020 同源同表；payable_balance 模板的 WHERE 条件从 ACPTK 改为 ACPLB</t>
         </is>
       </c>
     </row>
